--- a/data/preseason2026/2026-2027 TPBL 季前熱身賽球員數據表 - 新竹御嵿攻城獅.xlsx
+++ b/data/preseason2026/2026-2027 TPBL 季前熱身賽球員數據表 - 新竹御嵿攻城獅.xlsx
@@ -5,8 +5,8 @@
   <sheets>
     <sheet state="visible" name="平均數據" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="球員進階數據 (Advanced Stats)" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="2026.10.10 G01 vs 高雄全家海神" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="2026.10.11 G02 vs 新北國王" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="2026.10.10 G04 攻城獅 vs 海神" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="2026.10.11 G07 國王 vs 攻城獅" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -67,6 +67,9 @@
     <t>罰球出手</t>
   </si>
   <si>
+    <t>2026-2027 賽季 新竹御嵿攻城獅 (TPBL) 季前熱身賽球員攻守數據與進階陣容分析表 (全2戰累積版)</t>
+  </si>
+  <si>
     <t>罰球%</t>
   </si>
   <si>
@@ -91,9 +94,6 @@
     <t>TOV%</t>
   </si>
   <si>
-    <t>2026-2027 賽季 新竹御嵿攻城獅 (TPBL) 季前熱身賽球員攻守數據與進階陣容分析表 (全2戰累積版)</t>
-  </si>
-  <si>
     <t>GmSc</t>
   </si>
   <si>
@@ -121,217 +121,262 @@
     <t>PF</t>
   </si>
   <si>
+    <t>註：採計TPBL 2026-2027 季前熱身賽官方電子紀錄攻守數據。數據包含傳統攻守、進階指標及 PBP 無換人時間段陣容分析。</t>
+  </si>
+  <si>
     <t>辛巴 (Sim Bhullar)</t>
   </si>
   <si>
     <t>C</t>
   </si>
   <si>
-    <t>註：採計TPBL 2026-2027 季前熱身賽官方電子紀錄攻守數據。數據包含傳統攻守、進階指標及 PBP 無換人時間段陣容分析。</t>
-  </si>
-  <si>
     <t>德魯 (Drew Pember)</t>
   </si>
   <si>
     <t>F</t>
   </si>
   <si>
+    <t>本土/洋將</t>
+  </si>
+  <si>
+    <t>在台年資</t>
+  </si>
+  <si>
+    <t>時間[分]</t>
+  </si>
+  <si>
+    <t>得分</t>
+  </si>
+  <si>
     <t>陳力生 (Chen Li-Sheng)</t>
   </si>
   <si>
     <t>G/PG</t>
   </si>
   <si>
+    <t>兩分命中</t>
+  </si>
+  <si>
+    <t>兩分出手</t>
+  </si>
+  <si>
+    <t>兩分%</t>
+  </si>
+  <si>
+    <t>進攻籃板</t>
+  </si>
+  <si>
+    <t>防守籃板</t>
+  </si>
+  <si>
+    <t>籃板</t>
+  </si>
+  <si>
+    <t>助攻</t>
+  </si>
+  <si>
     <t>曾柏喻 (Tseng Po-Yu)</t>
   </si>
   <si>
+    <t>2026-2027 賽季 新竹御嵿攻城獅 (TPBL) 季前熱身賽單場球員攻守數據表 (110 : 134 負 高雄全家海神)</t>
+  </si>
+  <si>
+    <t>抄截</t>
+  </si>
+  <si>
+    <t>阻攻</t>
+  </si>
+  <si>
     <t>G/SG</t>
   </si>
   <si>
-    <t>本土/洋將</t>
+    <t>失誤</t>
+  </si>
+  <si>
+    <t>犯規</t>
+  </si>
+  <si>
+    <t>EFF</t>
+  </si>
+  <si>
+    <t>註：採計TPBL 2026-2027 季前熱身賽官方電子紀錄攻守數據。比賽日期：2026年10月10日，地點：和平籃球館。</t>
+  </si>
+  <si>
+    <t>蔡宸綱 (Tsai Chen-Kang)</t>
+  </si>
+  <si>
+    <t>F/PF</t>
+  </si>
+  <si>
+    <t>投籃熱區與進攻特徵分佈</t>
+  </si>
+  <si>
+    <t>備註 / 熱身賽表現重點</t>
+  </si>
+  <si>
+    <t>盧冠軒 (Lu Kuan-Hsuan)</t>
+  </si>
+  <si>
+    <t>累計在場時間</t>
+  </si>
+  <si>
+    <t>累計On_ORtg</t>
+  </si>
+  <si>
+    <t>累計On_DRtg</t>
+  </si>
+  <si>
+    <t>累計On_NetRtg</t>
+  </si>
+  <si>
+    <t>累計Off_NetRtg</t>
+  </si>
+  <si>
+    <t>賽季淨影響力(Diff)</t>
   </si>
   <si>
     <t>2026-2027 賽季 新竹御嵿攻城獅 (TPBL) 季前熱身賽單場球員攻守數據表 (97 : 100 負 新北國王)</t>
   </si>
   <si>
-    <t>在台年資</t>
-  </si>
-  <si>
-    <t>時間[分]</t>
-  </si>
-  <si>
-    <t>得分</t>
+    <t>五人陣容組合</t>
+  </si>
+  <si>
+    <t>賽季累計時間</t>
+  </si>
+  <si>
+    <t>累計正負值(+/-)</t>
+  </si>
+  <si>
+    <t>Lineup ORtg</t>
+  </si>
+  <si>
+    <t>Lineup DRtg</t>
+  </si>
+  <si>
+    <t>王律翔 (Wang Lu-Hsiang)</t>
+  </si>
+  <si>
+    <t>Lineup NetRtg</t>
+  </si>
+  <si>
+    <t>G</t>
   </si>
   <si>
     <t>註：採計TPBL 2026-2027 季前熱身賽官方電子紀錄攻守數據。比賽日期：2026年10月11日，地點：和平籃球館。</t>
   </si>
   <si>
-    <t>蔡宸綱 (Tsai Chen-Kang)</t>
-  </si>
-  <si>
-    <t>F/PF</t>
-  </si>
-  <si>
-    <t>兩分命中</t>
-  </si>
-  <si>
-    <t>兩分出手</t>
-  </si>
-  <si>
-    <t>兩分%</t>
-  </si>
-  <si>
-    <t>進攻籃板</t>
-  </si>
-  <si>
-    <t>防守籃板</t>
-  </si>
-  <si>
-    <t>盧冠軒 (Lu Kuan-Hsuan)</t>
-  </si>
-  <si>
-    <t>籃板</t>
-  </si>
-  <si>
-    <t>助攻</t>
-  </si>
-  <si>
-    <t>抄截</t>
-  </si>
-  <si>
-    <t>阻攻</t>
-  </si>
-  <si>
-    <t>失誤</t>
-  </si>
-  <si>
-    <t>犯規</t>
-  </si>
-  <si>
-    <t>EFF</t>
-  </si>
-  <si>
-    <t>王律翔 (Wang Lu-Hsiang)</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>2026-2027 賽季 新竹御嵿攻城獅 (TPBL) 季前熱身賽單場球員攻守數據表 (110 : 134 負 高雄全家海神)</t>
+    <t>洋將搭檔組合</t>
+  </si>
+  <si>
+    <t>共同時間</t>
+  </si>
+  <si>
+    <t>累計(+/-)</t>
+  </si>
+  <si>
+    <t>攻守特徵與搭配建議</t>
+  </si>
+  <si>
+    <t>+/-</t>
   </si>
   <si>
     <t>奧獅頓 (Justin Alston)</t>
   </si>
   <si>
-    <t>+/-</t>
-  </si>
-  <si>
-    <t>投籃熱區與進攻特徵分佈</t>
-  </si>
-  <si>
-    <t>備註 / 熱身賽表現重點</t>
+    <t>2年</t>
+  </si>
+  <si>
+    <t>備註 / 單場表現重點</t>
+  </si>
+  <si>
+    <t>時間</t>
+  </si>
+  <si>
+    <t>On_ORtg</t>
+  </si>
+  <si>
+    <t>On_DRtg</t>
+  </si>
+  <si>
+    <t>On_NetRtg</t>
   </si>
   <si>
     <t>蘇奕晉 (Su Yi-Chin)</t>
   </si>
   <si>
-    <t>備註 / 單場表現重點</t>
-  </si>
-  <si>
-    <t>註：採計TPBL 2026-2027 季前熱身賽官方電子紀錄攻守數據。比賽日期：2026年10月10日，地點：和平籃球館。</t>
-  </si>
-  <si>
-    <t>累計在場時間</t>
-  </si>
-  <si>
-    <t>累計On_ORtg</t>
+    <t>Off_NetRtg</t>
+  </si>
+  <si>
+    <t>Diff</t>
   </si>
   <si>
     <t>傅友 (Nicholas Fu)</t>
   </si>
   <si>
-    <t>累計On_DRtg</t>
-  </si>
-  <si>
-    <t>累計On_NetRtg</t>
-  </si>
-  <si>
-    <t>累計Off_NetRtg</t>
-  </si>
-  <si>
-    <t>時間</t>
-  </si>
-  <si>
-    <t>賽季淨影響力(Diff)</t>
-  </si>
-  <si>
-    <t>On_ORtg</t>
-  </si>
-  <si>
-    <t>五人陣容組合</t>
-  </si>
-  <si>
-    <t>On_DRtg</t>
-  </si>
-  <si>
-    <t>On_NetRtg</t>
-  </si>
-  <si>
-    <t>賽季累計時間</t>
-  </si>
-  <si>
-    <t>Off_NetRtg</t>
+    <t>突破與外線並重</t>
+  </si>
+  <si>
+    <t>高國豪離隊後強勢接棒本土一哥，兩戰狂轟40分，罰球12罰全中，關鍵追分箭頭</t>
+  </si>
+  <si>
+    <t>劉丞勳</t>
+  </si>
+  <si>
+    <t>焦點對位交鋒</t>
+  </si>
+  <si>
+    <t>備註</t>
   </si>
   <si>
     <t>朱雲豪 (Chu Yun-Hao)</t>
   </si>
   <si>
-    <t>累計正負值(+/-)</t>
-  </si>
-  <si>
-    <t>Diff</t>
-  </si>
-  <si>
     <t>F/SF</t>
   </si>
   <si>
-    <t>Lineup ORtg</t>
-  </si>
-  <si>
-    <t>Lineup DRtg</t>
-  </si>
-  <si>
-    <t>Lineup NetRtg</t>
-  </si>
-  <si>
-    <t>洋將搭檔組合</t>
+    <t>曾柏喻-劉丞勳-蔡宸綱-德魯-迪亞洛</t>
   </si>
   <si>
     <t>張庭瑋 (Ting-Wei Chang)</t>
   </si>
   <si>
-    <t>共同時間</t>
-  </si>
-  <si>
-    <t>累計(+/-)</t>
-  </si>
-  <si>
-    <t>攻守特徵與搭配建議</t>
+    <t>攻下全隊最高21分，罰球7罰7中，展現本土第一得分箭頭氣勢</t>
+  </si>
+  <si>
+    <t>陳力生-曾柏喻-劉丞勳-德魯-迪亞洛</t>
   </si>
   <si>
     <t>徐小龍 (Syu Siao-Long)</t>
   </si>
   <si>
-    <t>焦點對位交鋒</t>
-  </si>
-  <si>
-    <t>備註</t>
+    <t>迪亞洛 + 德魯 (運動鋒線搭檔)</t>
+  </si>
+  <si>
+    <t>劉丞勳在場對位賀丹 (28:43)</t>
+  </si>
+  <si>
+    <t>賀丹攻下 17 分但命中率受限，劉丞勳以 54.5% 命中率轟下 21 分展現對抗性</t>
   </si>
   <si>
     <t>梁瀚 (Liang Han)</t>
   </si>
   <si>
-    <t>2年</t>
+    <t>第1年</t>
+  </si>
+  <si>
+    <t>德魯拉開空間與迪亞洛禁區衝搶終結互補，攻防移動速度最佳</t>
+  </si>
+  <si>
+    <t>禁區終結</t>
+  </si>
+  <si>
+    <t>禁區強攻16投10中狂轟21分7籃板，終結效率極高</t>
+  </si>
+  <si>
+    <t>迪亞洛</t>
+  </si>
+  <si>
+    <t>陳力生-劉丞勳-蔡宸綱-德魯-辛巴</t>
   </si>
   <si>
     <t>本土一哥</t>
@@ -340,19 +385,25 @@
     <t>攻下19分5籃板3助攻3抄截，罰球5罰全中，正負值+1</t>
   </si>
   <si>
+    <t>劉丞勳下場休息 (11:17)</t>
+  </si>
+  <si>
+    <t>海神外線砲火由蘇文儒與于煥亞連續命中拉開比分</t>
+  </si>
+  <si>
     <t>曾柏喻</t>
   </si>
   <si>
-    <t>突破與外線並重</t>
-  </si>
-  <si>
-    <t>高國豪離隊後強勢接棒本土一哥，兩戰狂轟40分，罰球12罰全中，關鍵追分箭頭</t>
-  </si>
-  <si>
-    <t>曾柏喻-劉丞勳-蔡宸綱-德魯-迪亞洛</t>
-  </si>
-  <si>
-    <t>劉丞勳</t>
+    <t>8年</t>
+  </si>
+  <si>
+    <t>禁區強攻與籃下終結為主(兩分佔比100%)</t>
+  </si>
+  <si>
+    <t>前NBA長人兩戰場均19.5分7.5籃板1.5阻攻，禁區終結效率極高</t>
+  </si>
+  <si>
+    <t>德魯</t>
   </si>
   <si>
     <t>迪亞洛在場對位沃許本 (30:52)</t>
@@ -361,16 +412,49 @@
     <t>沃許本攻下 25 分 13 籃板，迪亞洛以 58.3% 命中率轟下 19 分 8 籃板對抗</t>
   </si>
   <si>
-    <t>第1年</t>
+    <t>禁區雙塔</t>
+  </si>
+  <si>
+    <t>減重回歸攻下14分5籃板，但陷入5次犯規麻煩</t>
+  </si>
+  <si>
+    <t>辛巴</t>
+  </si>
+  <si>
+    <t>陳力生-曾柏喻-劉丞勳-迪亞洛-辛巴</t>
+  </si>
+  <si>
+    <t>王律翔-盧冠軒-劉丞勳-奧獅頓-辛巴</t>
+  </si>
+  <si>
+    <t>單場戰術結論</t>
+  </si>
+  <si>
+    <t>劉丞勳與迪亞洛禁區合砍42分表現強勢，但辛巴在場時防守退防過慢，遭海神單場射進15記三分失134分。</t>
+  </si>
+  <si>
+    <t>3年</t>
+  </si>
+  <si>
+    <t>迪亞洛 + 辛巴 (禁區雙塔組合)</t>
   </si>
   <si>
     <t>禁區強攻</t>
   </si>
   <si>
+    <t>禁區護框與前場籃板強勢，但外圍防守與回防速度偏慢</t>
+  </si>
+  <si>
     <t>攻下19分8籃板2助攻1抄截，命中率近6成，正負值+5</t>
   </si>
   <si>
-    <t>迪亞洛</t>
+    <t>突破推進</t>
+  </si>
+  <si>
+    <t>首秀替補出賽攻下11分3籃板2助攻2抄截</t>
+  </si>
+  <si>
+    <t>陳力生</t>
   </si>
   <si>
     <t>曾柏喻-傅友-劉丞勳-迪亞洛-德魯</t>
@@ -382,7 +466,19 @@
     <t>國王由克雷格連續切入造成禁區犯規</t>
   </si>
   <si>
-    <t>迪亞洛 + 德魯 (運動鋒線搭檔)</t>
+    <t>禁區強攻為主</t>
+  </si>
+  <si>
+    <t>減重25kg回歸，兩戰兩分球10投9中命中率達9成，但陷入犯規麻煩</t>
+  </si>
+  <si>
+    <t>高砲塔前鋒</t>
+  </si>
+  <si>
+    <t>先發出賽貢獻9分4籃板2助攻，罰球5罰5中</t>
+  </si>
+  <si>
+    <t>陳力生-盧冠軒-蔡宸綱-奧獅頓-辛巴</t>
   </si>
   <si>
     <t>內外兼修</t>
@@ -391,19 +487,37 @@
     <t>高效砍下17分8籃板2助攻1抄截1阻攻，三分球3投2中</t>
   </si>
   <si>
-    <t>陳力生-盧冠軒-蔡宸綱-奧獅頓-辛巴</t>
-  </si>
-  <si>
-    <t>單場戰術結論</t>
+    <t>德魯 + 辛巴 (高低位搭配)</t>
+  </si>
+  <si>
+    <t>德魯外線投射能為辛巴拉出單打空間，但橫向換防容易遭對手後衛切入</t>
+  </si>
+  <si>
+    <t>空間四號</t>
+  </si>
+  <si>
+    <t>替補登場攻下9分2籃板1助攻</t>
   </si>
   <si>
     <t>攻城獅上半場防守奏效建立14分領先，但第三節外線防守交代不清遭國王一波流逆轉，年輕陣容展現拚勁。</t>
   </si>
   <si>
-    <t>德魯拉開空間與迪亞洛禁區衝搶終結互補，攻防移動速度最佳</t>
-  </si>
-  <si>
-    <t>3年</t>
+    <t>5年</t>
+  </si>
+  <si>
+    <t>外線高砲塔</t>
+  </si>
+  <si>
+    <t>先發大前鋒具備優異外線投射，兩戰三分球8投4中</t>
+  </si>
+  <si>
+    <t>中距離拋投</t>
+  </si>
+  <si>
+    <t>攻下9分2籃板2助攻1抄截</t>
+  </si>
+  <si>
+    <t>奧獅頓</t>
   </si>
   <si>
     <t>外線砲火</t>
@@ -412,37 +526,43 @@
     <t>飆進2記三分攻下15分6籃板3助攻0失誤</t>
   </si>
   <si>
-    <t>德魯</t>
-  </si>
-  <si>
-    <t>攻下全隊最高21分，罰球7罰7中，展現本土第一得分箭頭氣勢</t>
-  </si>
-  <si>
-    <t>禁區強攻與籃下終結為主(兩分佔比100%)</t>
-  </si>
-  <si>
-    <t>前NBA長人兩戰場均19.5分7.5籃板1.5阻攻，禁區終結效率極高</t>
+    <t>9年</t>
+  </si>
+  <si>
+    <t>外線射手</t>
+  </si>
+  <si>
+    <t>替補出賽投進1記三分球送出3次助攻</t>
+  </si>
+  <si>
+    <t>盧冠軒</t>
+  </si>
+  <si>
+    <t>持球推進</t>
   </si>
   <si>
     <t>替補奇兵</t>
   </si>
   <si>
+    <t>轉戰攻城獅表現搶眼，持球推進具侵略性，失誤控制待加強</t>
+  </si>
+  <si>
     <t>替補高效4投3中攻下9分2助攻1抄截，正負值+3</t>
   </si>
   <si>
     <t>傅友</t>
   </si>
   <si>
-    <t>陳力生-曾柏喻-劉丞勳-迪亞洛-辛巴</t>
-  </si>
-  <si>
-    <t>陳力生-曾柏喻-劉丞勳-德魯-迪亞洛</t>
-  </si>
-  <si>
-    <t>8年</t>
-  </si>
-  <si>
-    <t>迪亞洛 + 辛巴 (禁區雙塔組合)</t>
+    <t>後場輪替</t>
+  </si>
+  <si>
+    <t>先發登場投進1記三分攻下5分</t>
+  </si>
+  <si>
+    <t>籃板守護</t>
+  </si>
+  <si>
+    <t>抓下全隊最高12籃板(2前板)，但投籃手感低迷</t>
   </si>
   <si>
     <t>禁區百分百</t>
@@ -451,67 +571,58 @@
     <t>禁區4投全中攻下9分6籃板1抄截1阻攻</t>
   </si>
   <si>
-    <t>禁區護框與前場籃板強勢，但外圍防守與回防速度偏慢</t>
+    <t>10年</t>
   </si>
   <si>
     <t>蔡宸綱</t>
   </si>
   <si>
-    <t>劉丞勳在場對位賀丹 (28:43)</t>
-  </si>
-  <si>
-    <t>賀丹攻下 17 分但命中率受限，劉丞勳以 54.5% 命中率轟下 21 分展現對抗性</t>
-  </si>
-  <si>
-    <t>9年</t>
-  </si>
-  <si>
-    <t>外線射手</t>
+    <t>主力後場指揮官，中距離拋投與擋拆傳球穩定</t>
+  </si>
+  <si>
+    <t>老將替補</t>
+  </si>
+  <si>
+    <t>替補登場上籃攻下2分</t>
+  </si>
+  <si>
+    <t>新秀適應</t>
   </si>
   <si>
     <t>貢獻7分3籃板3助攻1抄截，投進1記三分</t>
   </si>
   <si>
-    <t>辛巴</t>
-  </si>
-  <si>
-    <t>禁區強攻為主</t>
-  </si>
-  <si>
-    <t>減重25kg回歸，兩戰兩分球10投9中命中率達9成，但陷入犯規麻煩</t>
-  </si>
-  <si>
-    <t>5年</t>
-  </si>
-  <si>
-    <t>禁區終結</t>
-  </si>
-  <si>
-    <t>禁區強攻16投10中狂轟21分7籃板，終結效率極高</t>
-  </si>
-  <si>
-    <t>陳力生-劉丞勳-蔡宸綱-德魯-辛巴</t>
-  </si>
-  <si>
-    <t>德魯 + 辛巴 (高低位搭配)</t>
+    <t>替補登場抓1籃板送出1助攻</t>
+  </si>
+  <si>
+    <t>本土年輕大前鋒，外圍具三分威脅，需注意犯規控制</t>
+  </si>
+  <si>
+    <t>6年</t>
+  </si>
+  <si>
+    <t>外線替補</t>
+  </si>
+  <si>
+    <t>替補登場抓1進攻籃板1助攻</t>
   </si>
   <si>
     <t>控導組織</t>
   </si>
   <si>
+    <t>外線手感低迷，但防守抄截敏銳，兩戰送出5次抄截</t>
+  </si>
+  <si>
     <t>先發送出5次助攻3籃板1抄截，正負值+12為全場最高</t>
   </si>
   <si>
-    <t>陳力生</t>
-  </si>
-  <si>
-    <t>劉丞勳下場休息 (11:17)</t>
-  </si>
-  <si>
-    <t>德魯外線投射能為辛巴拉出單打空間，但橫向換防容易遭對手後衛切入</t>
-  </si>
-  <si>
-    <t>海神外線砲火由蘇文儒與于煥亞連續命中拉開比分</t>
+    <t>未出賽</t>
+  </si>
+  <si>
+    <t>DNP / 新秀後衛未登錄出賽</t>
+  </si>
+  <si>
+    <t>DNP / 後衛替補輪休</t>
   </si>
   <si>
     <t>壓迫防守</t>
@@ -520,13 +631,19 @@
     <t>送出3次抄截3助攻，但發生5次失誤</t>
   </si>
   <si>
-    <t>禁區雙塔</t>
-  </si>
-  <si>
-    <t>減重回歸攻下14分5籃板，但陷入5次犯規麻煩</t>
-  </si>
-  <si>
-    <t>王律翔-盧冠軒-劉丞勳-奧獅頓-辛巴</t>
+    <t>DNP / 前鋒未出賽</t>
+  </si>
+  <si>
+    <t>團隊總計</t>
+  </si>
+  <si>
+    <t>新加盟後衛替補出賽調節戰力</t>
+  </si>
+  <si>
+    <t>16名球員</t>
+  </si>
+  <si>
+    <t>―</t>
   </si>
   <si>
     <t>替補輪替</t>
@@ -535,13 +652,16 @@
     <t>替補出場抓1進攻籃板</t>
   </si>
   <si>
-    <t>外線高砲塔</t>
-  </si>
-  <si>
-    <t>先發大前鋒具備優異外線投射，兩戰三分球8投4中</t>
-  </si>
-  <si>
-    <t>劉丞勳與迪亞洛禁區合砍42分表現強勢，但辛巴在場時防守退防過慢，遭海神單場射進15記三分失134分。</t>
+    <t>團隊單場統計</t>
+  </si>
+  <si>
+    <t>兩分球命中率59%，但三分出手僅18.2%外線失準，第四節遭海神狂轟40分崩盤</t>
+  </si>
+  <si>
+    <t>籃板保護</t>
+  </si>
+  <si>
+    <t>籃板保護出色，但投籃手感嚴重失準</t>
   </si>
   <si>
     <t>替補前鋒</t>
@@ -550,148 +670,28 @@
     <t>手感欠佳7投0中，得1籃板1助攻</t>
   </si>
   <si>
-    <t>10年</t>
-  </si>
-  <si>
-    <t>未出賽</t>
-  </si>
-  <si>
-    <t>突破推進</t>
+    <t>老將調節</t>
+  </si>
+  <si>
+    <t>老將替補登場調節禁區肉搏</t>
   </si>
   <si>
     <t>DNP / 本場輪休</t>
   </si>
   <si>
-    <t>首秀替補出賽攻下11分3籃板2助攻2抄截</t>
-  </si>
-  <si>
-    <t>6年</t>
-  </si>
-  <si>
-    <t>持球推進</t>
-  </si>
-  <si>
-    <t>轉戰攻城獅表現搶眼，持球推進具侵略性，失誤控制待加強</t>
-  </si>
-  <si>
-    <t>高砲塔前鋒</t>
-  </si>
-  <si>
-    <t>DNP / 新秀後衛未登錄出賽</t>
-  </si>
-  <si>
-    <t>先發出賽貢獻9分4籃板2助攻，罰球5罰5中</t>
-  </si>
-  <si>
-    <t>空間四號</t>
-  </si>
-  <si>
-    <t>替補登場攻下9分2籃板1助攻</t>
-  </si>
-  <si>
-    <t>DNP / 後衛替補輪休</t>
-  </si>
-  <si>
-    <t>中距離拋投</t>
-  </si>
-  <si>
-    <t>主力後場指揮官，中距離拋投與擋拆傳球穩定</t>
-  </si>
-  <si>
-    <t>攻下9分2籃板2助攻1抄截</t>
-  </si>
-  <si>
-    <t>奧獅頓</t>
-  </si>
-  <si>
-    <t>DNP / 前鋒未出賽</t>
-  </si>
-  <si>
-    <t>團隊總計</t>
-  </si>
-  <si>
-    <t>16名球員</t>
-  </si>
-  <si>
-    <t>―</t>
-  </si>
-  <si>
-    <t>替補出賽投進1記三分球送出3次助攻</t>
-  </si>
-  <si>
-    <t>盧冠軒</t>
-  </si>
-  <si>
-    <t>團隊單場統計</t>
+    <t>新秀登場適應職業對抗強度</t>
+  </si>
+  <si>
+    <t>外線替補登場調節手感</t>
+  </si>
+  <si>
+    <t>團隊全場戰力總計</t>
+  </si>
+  <si>
+    <t>熱身賽0勝2敗，團隊三分出手比僅26.9%聯盟最低，進攻效率99.4，防守效率112.4，淨效率-13.0</t>
   </si>
   <si>
     <t>上半場領先14分，但第三節遭國王一波流逆轉，末節追至3分惜敗</t>
-  </si>
-  <si>
-    <t>本土年輕大前鋒，外圍具三分威脅，需注意犯規控制</t>
-  </si>
-  <si>
-    <t>後場輪替</t>
-  </si>
-  <si>
-    <t>先發登場投進1記三分攻下5分</t>
-  </si>
-  <si>
-    <t>籃板守護</t>
-  </si>
-  <si>
-    <t>抓下全隊最高12籃板(2前板)，但投籃手感低迷</t>
-  </si>
-  <si>
-    <t>外線手感低迷，但防守抄截敏銳，兩戰送出5次抄截</t>
-  </si>
-  <si>
-    <t>老將替補</t>
-  </si>
-  <si>
-    <t>替補登場上籃攻下2分</t>
-  </si>
-  <si>
-    <t>新秀適應</t>
-  </si>
-  <si>
-    <t>替補登場抓1籃板送出1助攻</t>
-  </si>
-  <si>
-    <t>外線替補</t>
-  </si>
-  <si>
-    <t>替補登場抓1進攻籃板1助攻</t>
-  </si>
-  <si>
-    <t>新加盟後衛替補出賽調節戰力</t>
-  </si>
-  <si>
-    <t>籃板保護</t>
-  </si>
-  <si>
-    <t>籃板保護出色，但投籃手感嚴重失準</t>
-  </si>
-  <si>
-    <t>兩分球命中率59%，但三分出手僅18.2%外線失準，第四節遭海神狂轟40分崩盤</t>
-  </si>
-  <si>
-    <t>老將調節</t>
-  </si>
-  <si>
-    <t>老將替補登場調節禁區肉搏</t>
-  </si>
-  <si>
-    <t>新秀登場適應職業對抗強度</t>
-  </si>
-  <si>
-    <t>外線替補登場調節手感</t>
-  </si>
-  <si>
-    <t>團隊全場戰力總計</t>
-  </si>
-  <si>
-    <t>熱身賽0勝2敗，團隊三分出手比僅26.9%聯盟最低，進攻效率99.4，防守效率112.4，淨效率-13.0</t>
   </si>
 </sst>
 </file>
@@ -813,11 +813,14 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf quotePrefix="1" borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -825,20 +828,17 @@
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="2" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -857,8 +857,8 @@
       <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF003366"/>
-          <bgColor rgb="FF003366"/>
+          <fgColor rgb="FF1D3A8A"/>
+          <bgColor rgb="FF1D3A8A"/>
         </patternFill>
       </fill>
       <border/>
@@ -867,8 +867,8 @@
       <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF1D3A8A"/>
-          <bgColor rgb="FF1D3A8A"/>
+          <fgColor rgb="FFF2F4F5"/>
+          <bgColor rgb="FFF2F4F5"/>
         </patternFill>
       </fill>
       <border/>
@@ -887,8 +887,8 @@
       <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF2F4F5"/>
-          <bgColor rgb="FFF2F4F5"/>
+          <fgColor rgb="FF003366"/>
+          <bgColor rgb="FF003366"/>
         </patternFill>
       </fill>
       <border/>
@@ -905,68 +905,68 @@
     </dxf>
   </dxfs>
   <tableStyles count="13">
-    <tableStyle count="3" pivot="0" name="球員進階數據 (Advanced Stats)-style">
-      <tableStyleElement dxfId="2" type="headerRow"/>
-      <tableStyleElement dxfId="4" type="firstRowStripe"/>
+    <tableStyle count="3" pivot="0" name="平均數據-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="平均數據-style">
-      <tableStyleElement dxfId="2" type="headerRow"/>
-      <tableStyleElement dxfId="4" type="firstRowStripe"/>
+    <tableStyle count="3" pivot="0" name="球員進階數據 (Advanced Stats)-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="2026.10.11 G02 vs 新北國王-style">
+    <tableStyle count="3" pivot="0" name="平均數據-style 2">
       <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    </tableStyle>
+    <tableStyle count="3" pivot="0" name="2026.10.11 G07 國王 vs 攻城獅-style">
+      <tableStyleElement dxfId="4" type="headerRow"/>
       <tableStyleElement dxfId="3" type="firstRowStripe"/>
       <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="2026.10.10 G01 vs 高雄全家海神-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
+    <tableStyle count="3" pivot="0" name="2026.10.10 G04 攻城獅 vs 海神-style">
+      <tableStyleElement dxfId="4" type="headerRow"/>
       <tableStyleElement dxfId="3" type="firstRowStripe"/>
       <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="平均數據-style 2">
-      <tableStyleElement dxfId="2" type="headerRow"/>
-      <tableStyleElement dxfId="4" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-    </tableStyle>
     <tableStyle count="3" pivot="0" name="平均數據-style 3">
-      <tableStyleElement dxfId="2" type="headerRow"/>
-      <tableStyleElement dxfId="4" type="firstRowStripe"/>
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
     <tableStyle count="3" pivot="0" name="平均數據-style 4">
-      <tableStyleElement dxfId="2" type="headerRow"/>
-      <tableStyleElement dxfId="4" type="firstRowStripe"/>
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="2026.10.11 G02 vs 新北國王-style 2">
-      <tableStyleElement dxfId="1" type="headerRow"/>
+    <tableStyle count="3" pivot="0" name="2026.10.10 G04 攻城獅 vs 海神-style 2">
+      <tableStyleElement dxfId="4" type="headerRow"/>
       <tableStyleElement dxfId="3" type="firstRowStripe"/>
       <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="2026.10.11 G02 vs 新北國王-style 3">
-      <tableStyleElement dxfId="1" type="headerRow"/>
+    <tableStyle count="3" pivot="0" name="2026.10.10 G04 攻城獅 vs 海神-style 3">
+      <tableStyleElement dxfId="4" type="headerRow"/>
       <tableStyleElement dxfId="3" type="firstRowStripe"/>
       <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="2026.10.11 G02 vs 新北國王-style 4">
-      <tableStyleElement dxfId="1" type="headerRow"/>
+    <tableStyle count="3" pivot="0" name="2026.10.10 G04 攻城獅 vs 海神-style 4">
+      <tableStyleElement dxfId="4" type="headerRow"/>
       <tableStyleElement dxfId="3" type="firstRowStripe"/>
       <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="2026.10.10 G01 vs 高雄全家海神-style 2">
-      <tableStyleElement dxfId="1" type="headerRow"/>
+    <tableStyle count="3" pivot="0" name="2026.10.11 G07 國王 vs 攻城獅-style 2">
+      <tableStyleElement dxfId="4" type="headerRow"/>
       <tableStyleElement dxfId="3" type="firstRowStripe"/>
       <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="2026.10.10 G01 vs 高雄全家海神-style 3">
-      <tableStyleElement dxfId="1" type="headerRow"/>
+    <tableStyle count="3" pivot="0" name="2026.10.11 G07 國王 vs 攻城獅-style 3">
+      <tableStyleElement dxfId="4" type="headerRow"/>
       <tableStyleElement dxfId="3" type="firstRowStripe"/>
       <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="2026.10.10 G01 vs 高雄全家海神-style 4">
-      <tableStyleElement dxfId="1" type="headerRow"/>
+    <tableStyle count="3" pivot="0" name="2026.10.11 G07 國王 vs 攻城獅-style 4">
+      <tableStyleElement dxfId="4" type="headerRow"/>
       <tableStyleElement dxfId="3" type="firstRowStripe"/>
       <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
@@ -995,7 +995,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A4:AI21" displayName="Table_3" name="Table_3" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A4:AI21" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="35">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1043,7 +1043,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A4:AI21" displayName="Table_4" name="Table_4" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A4:AI21" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="35">
     <tableColumn name="背號" id="1"/>
     <tableColumn name="球員名" id="2"/>
@@ -1081,12 +1081,12 @@
     <tableColumn name="投籃熱區與進攻特徵分佈" id="34"/>
     <tableColumn name="備註 / 單場表現重點" id="35"/>
   </tableColumns>
-  <tableStyleInfo name="2026.10.11 G02 vs 新北國王-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="2026.10.11 G07 國王 vs 攻城獅-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AK4:AQ12" displayName="Table_8" name="Table_8" id="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AK4:AQ12" displayName="Table_11" name="Table_11" id="11">
   <tableColumns count="7">
     <tableColumn name="球員名" id="1"/>
     <tableColumn name="時間" id="2"/>
@@ -1096,12 +1096,12 @@
     <tableColumn name="Off_NetRtg" id="6"/>
     <tableColumn name="Diff" id="7"/>
   </tableColumns>
-  <tableStyleInfo name="2026.10.11 G02 vs 新北國王-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="2026.10.11 G07 國王 vs 攻城獅-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="AS4:AX7" displayName="Table_9" name="Table_9" id="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="AS4:AX7" displayName="Table_12" name="Table_12" id="12">
   <tableColumns count="6">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1110,7 +1110,7 @@
     <tableColumn name="Column5" id="5"/>
     <tableColumn name="Column6" id="6"/>
   </tableColumns>
-  <tableStyleInfo name="2026.10.11 G02 vs 新北國王-style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="2026.10.11 G07 國王 vs 攻城獅-style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" headerRowCount="1"/>
@@ -1120,12 +1120,12 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AZ4:BA7" displayName="Table_11" name="Table_11" id="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AZ4:BA7" displayName="Table_13" name="Table_13" id="13">
   <tableColumns count="2">
     <tableColumn name="焦點對位交鋒" id="1"/>
     <tableColumn name="備註" id="2"/>
   </tableColumns>
-  <tableStyleInfo name="2026.10.11 G02 vs 新北國王-style 4" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="2026.10.11 G07 國王 vs 攻城獅-style 4" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -1174,7 +1174,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:Z19" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:Z19" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="26">
     <tableColumn name="球隊" id="1"/>
     <tableColumn name="背號" id="2"/>
@@ -1208,7 +1208,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A4:AI21" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A4:AI21" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="35">
     <tableColumn name="背號" id="1"/>
     <tableColumn name="球員名" id="2"/>
@@ -1246,12 +1246,12 @@
     <tableColumn name="投籃熱區與進攻特徵分佈" id="34"/>
     <tableColumn name="備註 / 單場表現重點" id="35"/>
   </tableColumns>
-  <tableStyleInfo name="2026.10.10 G01 vs 高雄全家海神-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="2026.10.10 G04 攻城獅 vs 海神-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AK4:AQ12" displayName="Table_10" name="Table_10" id="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AK4:AQ12" displayName="Table_8" name="Table_8" id="8">
   <tableColumns count="7">
     <tableColumn name="球員名" id="1"/>
     <tableColumn name="時間" id="2"/>
@@ -1261,12 +1261,12 @@
     <tableColumn name="Off_NetRtg" id="6"/>
     <tableColumn name="Diff" id="7"/>
   </tableColumns>
-  <tableStyleInfo name="2026.10.10 G01 vs 高雄全家海神-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="2026.10.10 G04 攻城獅 vs 海神-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="AS4:AX7" displayName="Table_12" name="Table_12" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="AS4:AX7" displayName="Table_9" name="Table_9" id="9">
   <tableColumns count="6">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1275,7 +1275,7 @@
     <tableColumn name="Column5" id="5"/>
     <tableColumn name="Column6" id="6"/>
   </tableColumns>
-  <tableStyleInfo name="2026.10.10 G01 vs 高雄全家海神-style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="2026.10.10 G04 攻城獅 vs 海神-style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" headerRowCount="1"/>
@@ -1285,12 +1285,12 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AZ4:BA7" displayName="Table_13" name="Table_13" id="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AZ4:BA7" displayName="Table_10" name="Table_10" id="10">
   <tableColumns count="2">
     <tableColumn name="焦點對位交鋒" id="1"/>
     <tableColumn name="備註" id="2"/>
   </tableColumns>
-  <tableStyleInfo name="2026.10.10 G01 vs 高雄全家海神-style 4" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="2026.10.10 G04 攻城獅 vs 海神-style 4" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -1497,7 +1497,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1561,7 +1561,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1631,22 +1631,22 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>9</v>
@@ -1658,13 +1658,13 @@
         <v>11</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>12</v>
@@ -1682,118 +1682,118 @@
         <v>16</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="Z4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="AA4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="AB4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="AC4" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="Z4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC4" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="AD4" s="8" t="str">
         <v>#ERROR!</v>
       </c>
       <c r="AE4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG4" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AH4" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="AI4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AJ4" s="10"/>
+        <v>65</v>
+      </c>
+      <c r="AJ4" s="9"/>
       <c r="AK4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM4" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AO4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AQ4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR4" s="9"/>
+      <c r="AS4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT4" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AM4" s="3" t="s">
+      <c r="AU4" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="AN4" s="3" t="s">
+      <c r="AV4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW4" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="AO4" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AP4" s="3" t="s">
+      <c r="AX4" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="AQ4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AR4" s="10"/>
-      <c r="AS4" s="3" t="s">
+      <c r="AY4" s="9"/>
+      <c r="AZ4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="BA4" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="AT4" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU4" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AV4" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AW4" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="AX4" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AY4" s="10"/>
-      <c r="AZ4" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="BA4" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="BB4" s="3" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="BC4" s="3" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="BD4" s="3" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="BE4" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="BF4" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="BG4" s="10"/>
-      <c r="BH4" s="10"/>
+        <v>86</v>
+      </c>
+      <c r="BG4" s="9"/>
+      <c r="BH4" s="9"/>
     </row>
     <row r="5">
       <c r="A5" s="4">
@@ -1809,12 +1809,12 @@
         <v>31</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="F5" s="4">
         <v>2.0</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="12">
         <v>1.3243055555555556</v>
       </c>
       <c r="H5" s="4">
@@ -1896,15 +1896,15 @@
         <v>1.0</v>
       </c>
       <c r="AH5" s="4" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AI5" s="4" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK5" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL5" s="15">
+        <v>101</v>
+      </c>
+      <c r="AL5" s="12">
         <v>2.6486111111111112</v>
       </c>
       <c r="AM5" s="4">
@@ -1919,16 +1919,16 @@
       <c r="AP5" s="4">
         <v>-24.5</v>
       </c>
-      <c r="AQ5" s="19">
+      <c r="AQ5" s="17">
         <v>22.8</v>
       </c>
       <c r="AS5" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="AT5" s="20">
+        <v>106</v>
+      </c>
+      <c r="AT5" s="19">
         <v>0.65625</v>
       </c>
-      <c r="AU5" s="19">
+      <c r="AU5" s="17">
         <v>8</v>
       </c>
       <c r="AV5" s="4">
@@ -1937,16 +1937,16 @@
       <c r="AW5" s="4">
         <v>103.5</v>
       </c>
-      <c r="AX5" s="19">
+      <c r="AX5" s="17">
         <v>10.7</v>
       </c>
       <c r="AZ5" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="BA5" s="15">
+        <v>111</v>
+      </c>
+      <c r="BA5" s="12">
         <v>1.34375</v>
       </c>
-      <c r="BB5" s="19">
+      <c r="BB5" s="17">
         <v>4</v>
       </c>
       <c r="BC5" s="4">
@@ -1955,11 +1955,11 @@
       <c r="BD5" s="4">
         <v>105.2</v>
       </c>
-      <c r="BE5" s="19">
+      <c r="BE5" s="17">
         <v>4.3</v>
       </c>
       <c r="BF5" s="4" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6">
@@ -1981,7 +1981,7 @@
       <c r="F6" s="4">
         <v>2.0</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="12">
         <v>1.0104166666666667</v>
       </c>
       <c r="H6" s="4">
@@ -2063,15 +2063,15 @@
         <v>0.33</v>
       </c>
       <c r="AH6" s="4" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="AI6" s="4" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="AK6" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL6" s="15">
+        <v>129</v>
+      </c>
+      <c r="AL6" s="12">
         <v>1.7083333333333333</v>
       </c>
       <c r="AM6" s="4">
@@ -2086,16 +2086,16 @@
       <c r="AP6" s="4">
         <v>-19.8</v>
       </c>
-      <c r="AQ6" s="19">
+      <c r="AQ6" s="17">
         <v>16.1</v>
       </c>
       <c r="AS6" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="AT6" s="20">
+        <v>135</v>
+      </c>
+      <c r="AT6" s="19">
         <v>0.5138888888888888</v>
       </c>
-      <c r="AU6" s="19">
+      <c r="AU6" s="17">
         <v>2</v>
       </c>
       <c r="AV6" s="4">
@@ -2104,13 +2104,13 @@
       <c r="AW6" s="4">
         <v>105.0</v>
       </c>
-      <c r="AX6" s="19">
+      <c r="AX6" s="17">
         <v>1.8</v>
       </c>
       <c r="AZ6" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="BA6" s="15">
+        <v>140</v>
+      </c>
+      <c r="BA6" s="12">
         <v>1.0277777777777777</v>
       </c>
       <c r="BB6" s="4">
@@ -2126,7 +2126,7 @@
         <v>-7.8</v>
       </c>
       <c r="BF6" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7">
@@ -2134,21 +2134,21 @@
         <v>35.0</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="F7" s="4">
         <v>2.0</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="19">
         <v>0.9027777777777778</v>
       </c>
       <c r="H7" s="4">
@@ -2230,15 +2230,15 @@
         <v>0.33</v>
       </c>
       <c r="AH7" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="AI7" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="AK7" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL7" s="15">
+        <v>125</v>
+      </c>
+      <c r="AL7" s="12">
         <v>1.3611111111111112</v>
       </c>
       <c r="AM7" s="4">
@@ -2253,13 +2253,13 @@
       <c r="AP7" s="4">
         <v>-17.2</v>
       </c>
-      <c r="AQ7" s="19">
+      <c r="AQ7" s="17">
         <v>11.4</v>
       </c>
       <c r="AS7" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AT7" s="20">
+        <v>154</v>
+      </c>
+      <c r="AT7" s="19">
         <v>0.4375</v>
       </c>
       <c r="AU7" s="4">
@@ -2275,9 +2275,9 @@
         <v>-25.7</v>
       </c>
       <c r="AZ7" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="BA7" s="20">
+        <v>157</v>
+      </c>
+      <c r="BA7" s="19">
         <v>0.7638888888888888</v>
       </c>
       <c r="BB7" s="4">
@@ -2293,7 +2293,7 @@
         <v>-11.9</v>
       </c>
       <c r="BF7" s="4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8">
@@ -2310,12 +2310,12 @@
         <v>39</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="F8" s="4">
         <v>2.0</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="19">
         <v>0.8541666666666666</v>
       </c>
       <c r="H8" s="4">
@@ -2397,15 +2397,15 @@
         <v>4.0</v>
       </c>
       <c r="AH8" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="AI8" s="4" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="AK8" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL8" s="15">
+        <v>119</v>
+      </c>
+      <c r="AL8" s="12">
         <v>2.0208333333333335</v>
       </c>
       <c r="AM8" s="4">
@@ -2420,7 +2420,7 @@
       <c r="AP8" s="4">
         <v>-16.8</v>
       </c>
-      <c r="AQ8" s="19">
+      <c r="AQ8" s="17">
         <v>7.9</v>
       </c>
     </row>
@@ -2429,21 +2429,21 @@
         <v>3.0</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F9" s="4">
         <v>2.0</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="19">
         <v>0.7256944444444444</v>
       </c>
       <c r="H9" s="4">
@@ -2525,15 +2525,15 @@
         <v>0.83</v>
       </c>
       <c r="AH9" s="4" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="AI9" s="4" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="AK9" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL9" s="15">
+        <v>134</v>
+      </c>
+      <c r="AL9" s="12">
         <v>1.8055555555555556</v>
       </c>
       <c r="AM9" s="4">
@@ -2548,7 +2548,7 @@
       <c r="AP9" s="4">
         <v>-14.2</v>
       </c>
-      <c r="AQ9" s="19">
+      <c r="AQ9" s="17">
         <v>2.7</v>
       </c>
     </row>
@@ -2557,21 +2557,21 @@
         <v>7.0</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F10" s="4">
         <v>2.0</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="19">
         <v>0.6805555555555556</v>
       </c>
       <c r="H10" s="4">
@@ -2653,15 +2653,15 @@
         <v>1.75</v>
       </c>
       <c r="AH10" s="4" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="AI10" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="AK10" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL10" s="15">
+        <v>146</v>
+      </c>
+      <c r="AL10" s="12">
         <v>1.4513888888888888</v>
       </c>
       <c r="AM10" s="4">
@@ -2685,21 +2685,21 @@
         <v>17.0</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F11" s="4">
         <v>2.0</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="19">
         <v>0.6180555555555556</v>
       </c>
       <c r="H11" s="4">
@@ -2781,15 +2781,15 @@
         <v>4.0</v>
       </c>
       <c r="AH11" s="4" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="AI11" s="4" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="AK11" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="AL11" s="15">
+        <v>186</v>
+      </c>
+      <c r="AL11" s="12">
         <v>1.2361111111111112</v>
       </c>
       <c r="AM11" s="4">
@@ -2813,21 +2813,21 @@
         <v>42.0</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="F12" s="4">
         <v>2.0</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="19">
         <v>0.8020833333333334</v>
       </c>
       <c r="H12" s="4">
@@ -2909,15 +2909,15 @@
         <v>1.0</v>
       </c>
       <c r="AH12" s="4" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="AI12" s="4" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="AK12" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="AL12" s="15">
+        <v>173</v>
+      </c>
+      <c r="AL12" s="12">
         <v>1.6041666666666667</v>
       </c>
       <c r="AM12" s="4">
@@ -2941,21 +2941,21 @@
         <v>8.0</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F13" s="4">
         <v>2.0</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="19">
         <v>0.5972222222222222</v>
       </c>
       <c r="H13" s="4">
@@ -3037,10 +3037,10 @@
         <v>0.0</v>
       </c>
       <c r="AH13" s="4" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="AI13" s="4" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14">
@@ -3048,7 +3048,7 @@
         <v>32.0</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>33</v>
@@ -3062,7 +3062,7 @@
       <c r="F14" s="4">
         <v>2.0</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="19">
         <v>0.7708333333333334</v>
       </c>
       <c r="H14" s="4">
@@ -3144,10 +3144,10 @@
         <v>1.0</v>
       </c>
       <c r="AH14" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AI14" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15">
@@ -3155,21 +3155,21 @@
         <v>41.0</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F15" s="4">
         <v>2.0</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="19">
         <v>0.2777777777777778</v>
       </c>
       <c r="H15" s="4">
@@ -3251,10 +3251,10 @@
         <v>0.0</v>
       </c>
       <c r="AH15" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AI15" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16">
@@ -3262,7 +3262,7 @@
         <v>14.0</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>30</v>
@@ -3276,7 +3276,7 @@
       <c r="F16" s="4">
         <v>2.0</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="19">
         <v>0.3854166666666667</v>
       </c>
       <c r="H16" s="4">
@@ -3358,10 +3358,10 @@
         <v>0.0</v>
       </c>
       <c r="AH16" s="4" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="AI16" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17">
@@ -3369,21 +3369,21 @@
         <v>28.0</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="F17" s="4">
         <v>2.0</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="19">
         <v>0.2708333333333333</v>
       </c>
       <c r="H17" s="4">
@@ -3465,10 +3465,10 @@
         <v>1.0</v>
       </c>
       <c r="AH17" s="4" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="AI17" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18">
@@ -3476,13 +3476,13 @@
         <v>6.0</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>115</v>
@@ -3490,7 +3490,7 @@
       <c r="F18" s="4">
         <v>0.0</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="19">
         <v>0.0</v>
       </c>
       <c r="H18" s="4">
@@ -3572,10 +3572,10 @@
         <v>0.0</v>
       </c>
       <c r="AH18" s="4" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="AI18" s="4" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19">
@@ -3583,21 +3583,21 @@
         <v>1.0</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="F19" s="4">
         <v>0.0</v>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="19">
         <v>0.0</v>
       </c>
       <c r="H19" s="4">
@@ -3679,10 +3679,10 @@
         <v>0.0</v>
       </c>
       <c r="AH19" s="4" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="AI19" s="4" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20">
@@ -3690,7 +3690,7 @@
         <v>25.0</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>30</v>
@@ -3699,12 +3699,12 @@
         <v>39</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="F20" s="4">
         <v>0.0</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="19">
         <v>0.0</v>
       </c>
       <c r="H20" s="4">
@@ -3786,32 +3786,32 @@
         <v>0.0</v>
       </c>
       <c r="AH20" s="4" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="AI20" s="4" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="F21" s="4">
         <v>2.0</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="12">
         <v>20.0</v>
       </c>
       <c r="H21" s="4">
@@ -3893,10 +3893,10 @@
         <v>0.89</v>
       </c>
       <c r="AH21" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="AI21" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="AI21" s="4" t="s">
-        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -3997,28 +3997,28 @@
         <v>16</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="3" t="s">
         <v>26</v>
@@ -4195,13 +4195,13 @@
         <v>35.0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6" s="4">
         <v>2.0</v>
@@ -4355,13 +4355,13 @@
         <v>3.0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F8" s="4">
         <v>2.0</v>
@@ -4435,13 +4435,13 @@
         <v>7.0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="F9" s="4">
         <v>2.0</v>
@@ -4515,13 +4515,13 @@
         <v>17.0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F10" s="4">
         <v>2.0</v>
@@ -4595,13 +4595,13 @@
         <v>42.0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="F11" s="4">
         <v>2.0</v>
@@ -4675,13 +4675,13 @@
         <v>8.0</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="F12" s="4">
         <v>2.0</v>
@@ -4755,7 +4755,7 @@
         <v>32.0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>33</v>
@@ -4835,13 +4835,13 @@
         <v>41.0</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F14" s="4">
         <v>2.0</v>
@@ -4915,7 +4915,7 @@
         <v>14.0</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>30</v>
@@ -4995,13 +4995,13 @@
         <v>28.0</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="F16" s="4">
         <v>2.0</v>
@@ -5075,13 +5075,13 @@
         <v>6.0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="F17" s="4">
         <v>0.0</v>
@@ -5155,13 +5155,13 @@
         <v>1.0</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="F18" s="4">
         <v>0.0</v>
@@ -5235,7 +5235,7 @@
         <v>25.0</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>30</v>
@@ -5368,12 +5368,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
@@ -5384,22 +5384,22 @@
         <v>3</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>9</v>
@@ -5411,13 +5411,13 @@
         <v>11</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="O4" s="7" t="s">
         <v>12</v>
@@ -5435,93 +5435,93 @@
         <v>16</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="W4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="X4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y4" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="7" t="s">
+      <c r="Z4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="W4" s="7" t="s">
+      <c r="AA4" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="X4" s="7" t="s">
+      <c r="AB4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="Y4" s="7" t="s">
+      <c r="AC4" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="Z4" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA4" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB4" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD4" s="9" t="s">
-        <v>69</v>
+      <c r="AD4" s="10" t="s">
+        <v>87</v>
       </c>
       <c r="AE4" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF4" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG4" s="7" t="s">
         <v>27</v>
       </c>
       <c r="AH4" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="AI4" s="7" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="AJ4" s="11"/>
       <c r="AK4" s="7" t="s">
         <v>3</v>
       </c>
       <c r="AL4" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM4" s="7" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AN4" s="7" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="AO4" s="7" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AP4" s="7" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="AQ4" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT4" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="AR4" s="11"/>
-      <c r="AS4" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="AT4" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="AU4" s="12" t="str">
+      <c r="AU4" s="13" t="str">
         <v>#ERROR!</v>
       </c>
       <c r="AV4" s="7" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AW4" s="7" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="AX4" s="7" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AY4" s="11"/>
       <c r="AZ4" s="7" t="s">
@@ -5532,2062 +5532,2062 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13">
+      <c r="A5" s="14">
         <v>13.0</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F5" s="13">
+      <c r="E5" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="14">
         <v>1.0</v>
       </c>
       <c r="G5" s="16">
         <v>1.1965277777777779</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="14">
         <v>21.0</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="14">
         <v>6.0</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="14">
         <v>11.0</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="18">
         <v>0.545</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="14">
         <v>4.0</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="14">
         <v>6.0</v>
       </c>
-      <c r="N5" s="17">
+      <c r="N5" s="18">
         <v>0.667</v>
       </c>
-      <c r="O5" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="P5" s="13">
+      <c r="O5" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="P5" s="14">
         <v>5.0</v>
       </c>
-      <c r="Q5" s="17">
+      <c r="Q5" s="18">
         <v>0.4</v>
       </c>
-      <c r="R5" s="13">
+      <c r="R5" s="14">
         <v>7.0</v>
       </c>
-      <c r="S5" s="13">
+      <c r="S5" s="14">
         <v>7.0</v>
       </c>
-      <c r="T5" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="U5" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="V5" s="13">
+      <c r="T5" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="U5" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="V5" s="14">
         <v>3.0</v>
       </c>
-      <c r="W5" s="13">
+      <c r="W5" s="14">
         <v>4.0</v>
       </c>
-      <c r="X5" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="Y5" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA5" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AB5" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AC5" s="13">
+      <c r="X5" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="Z5" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA5" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AB5" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AC5" s="14">
         <v>20.0</v>
       </c>
-      <c r="AD5" s="13">
+      <c r="AD5" s="14">
         <v>-9.0</v>
       </c>
-      <c r="AE5" s="17">
+      <c r="AE5" s="18">
         <v>0.636</v>
       </c>
-      <c r="AF5" s="17">
+      <c r="AF5" s="18">
         <v>0.746</v>
       </c>
-      <c r="AG5" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AH5" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="AI5" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="AK5" s="14" t="s">
-        <v>112</v>
+      <c r="AG5" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AH5" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="AI5" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="AK5" s="15" t="s">
+        <v>101</v>
       </c>
       <c r="AL5" s="16">
         <v>1.1965277777777779</v>
       </c>
-      <c r="AM5" s="13">
+      <c r="AM5" s="14">
         <v>105.0</v>
       </c>
-      <c r="AN5" s="13">
+      <c r="AN5" s="14">
         <v>118.5</v>
       </c>
-      <c r="AO5" s="13">
+      <c r="AO5" s="14">
         <v>-13.5</v>
       </c>
-      <c r="AP5" s="13">
+      <c r="AP5" s="14">
         <v>-38.5</v>
       </c>
-      <c r="AQ5" s="13">
+      <c r="AQ5" s="14">
         <v>25.0</v>
       </c>
-      <c r="AS5" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="AT5" s="18">
+      <c r="AS5" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="AT5" s="20">
         <v>0.3020833333333333</v>
       </c>
-      <c r="AU5" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AV5" s="13">
+      <c r="AU5" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AV5" s="14">
         <v>118.5</v>
       </c>
-      <c r="AW5" s="13">
+      <c r="AW5" s="14">
         <v>114.0</v>
       </c>
-      <c r="AX5" s="13">
+      <c r="AX5" s="14">
         <v>4.5</v>
       </c>
-      <c r="AZ5" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="BA5" s="14" t="s">
-        <v>148</v>
+      <c r="AZ5" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="BA5" s="15" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <v>33.0</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F6" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G6" s="18">
+      <c r="F6" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G6" s="20">
         <v>0.7347222222222223</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="14">
         <v>21.0</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="14">
         <v>10.0</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="14">
         <v>16.0</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="18">
         <v>0.625</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="14">
         <v>10.0</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="14">
         <v>16.0</v>
       </c>
-      <c r="N6" s="17">
+      <c r="N6" s="18">
         <v>0.625</v>
       </c>
-      <c r="O6" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P6" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Q6" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R6" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="S6" s="13">
+      <c r="O6" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P6" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q6" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R6" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="S6" s="14">
         <v>3.0</v>
       </c>
-      <c r="T6" s="17">
+      <c r="T6" s="18">
         <v>0.333</v>
       </c>
-      <c r="U6" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="V6" s="13">
+      <c r="U6" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="V6" s="14">
         <v>6.0</v>
       </c>
-      <c r="W6" s="13">
+      <c r="W6" s="14">
         <v>7.0</v>
       </c>
-      <c r="X6" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Y6" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z6" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA6" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AB6" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AC6" s="13">
+      <c r="X6" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Y6" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z6" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA6" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AB6" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AC6" s="14">
         <v>21.0</v>
       </c>
-      <c r="AD6" s="13">
+      <c r="AD6" s="14">
         <v>-16.0</v>
       </c>
-      <c r="AE6" s="17">
+      <c r="AE6" s="18">
         <v>0.625</v>
       </c>
-      <c r="AF6" s="17">
+      <c r="AF6" s="18">
         <v>0.606</v>
       </c>
-      <c r="AG6" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH6" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="AI6" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="AK6" s="14" t="s">
+      <c r="AG6" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH6" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI6" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="AL6" s="18">
+      <c r="AK6" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="AL6" s="20">
         <v>0.7347222222222223</v>
       </c>
-      <c r="AM6" s="13">
+      <c r="AM6" s="14">
         <v>104.2</v>
       </c>
-      <c r="AN6" s="13">
+      <c r="AN6" s="14">
         <v>120.0</v>
       </c>
-      <c r="AO6" s="13">
+      <c r="AO6" s="14">
         <v>-15.8</v>
       </c>
-      <c r="AP6" s="13">
+      <c r="AP6" s="14">
         <v>-28.5</v>
       </c>
-      <c r="AQ6" s="13">
+      <c r="AQ6" s="14">
         <v>12.7</v>
       </c>
-      <c r="AS6" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="AT6" s="18">
+      <c r="AS6" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="AT6" s="20">
         <v>0.2777777777777778</v>
       </c>
-      <c r="AU6" s="13">
+      <c r="AU6" s="14">
         <v>-2.0</v>
       </c>
-      <c r="AV6" s="13">
+      <c r="AV6" s="14">
         <v>106.0</v>
       </c>
-      <c r="AW6" s="13">
+      <c r="AW6" s="14">
         <v>110.5</v>
       </c>
-      <c r="AX6" s="13">
+      <c r="AX6" s="14">
         <v>-4.5</v>
       </c>
-      <c r="AZ6" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="BA6" s="14" t="s">
-        <v>165</v>
+      <c r="AZ6" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA6" s="15" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13">
+      <c r="A7" s="14">
         <v>35.0</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="14" t="s">
+      <c r="B7" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="F7" s="13">
+      <c r="D7" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="14">
         <v>1.0</v>
       </c>
       <c r="G7" s="16">
         <v>1.0916666666666666</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="14">
         <v>14.0</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="14">
         <v>5.0</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="14">
         <v>6.0</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="18">
         <v>0.833</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="14">
         <v>5.0</v>
       </c>
-      <c r="M7" s="13">
+      <c r="M7" s="14">
         <v>6.0</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="18">
         <v>0.833</v>
       </c>
-      <c r="O7" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P7" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Q7" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R7" s="13">
+      <c r="O7" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P7" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q7" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R7" s="14">
         <v>4.0</v>
       </c>
-      <c r="S7" s="13">
+      <c r="S7" s="14">
         <v>6.0</v>
       </c>
-      <c r="T7" s="17">
+      <c r="T7" s="18">
         <v>0.667</v>
       </c>
-      <c r="U7" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="V7" s="13">
+      <c r="U7" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="V7" s="14">
         <v>3.0</v>
       </c>
-      <c r="W7" s="13">
+      <c r="W7" s="14">
         <v>5.0</v>
       </c>
-      <c r="X7" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Y7" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z7" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA7" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AB7" s="13">
+      <c r="X7" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Y7" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z7" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA7" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AB7" s="14">
         <v>5.0</v>
       </c>
-      <c r="AC7" s="13">
+      <c r="AC7" s="14">
         <v>11.0</v>
       </c>
-      <c r="AD7" s="13">
+      <c r="AD7" s="14">
         <v>-6.0</v>
       </c>
-      <c r="AE7" s="17">
+      <c r="AE7" s="18">
         <v>0.833</v>
       </c>
-      <c r="AF7" s="17">
+      <c r="AF7" s="18">
         <v>0.81</v>
       </c>
-      <c r="AG7" s="13">
+      <c r="AG7" s="14">
         <v>0.5</v>
       </c>
-      <c r="AH7" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="AI7" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AK7" s="14" t="s">
-        <v>152</v>
+      <c r="AH7" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="AI7" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="AK7" s="15" t="s">
+        <v>134</v>
       </c>
       <c r="AL7" s="16">
         <v>1.0916666666666666</v>
       </c>
-      <c r="AM7" s="13">
+      <c r="AM7" s="14">
         <v>102.5</v>
       </c>
-      <c r="AN7" s="13">
+      <c r="AN7" s="14">
         <v>121.5</v>
       </c>
-      <c r="AO7" s="13">
+      <c r="AO7" s="14">
         <v>-19.0</v>
       </c>
-      <c r="AP7" s="13">
+      <c r="AP7" s="14">
         <v>-26.0</v>
       </c>
-      <c r="AQ7" s="13">
+      <c r="AQ7" s="14">
         <v>7.0</v>
       </c>
-      <c r="AS7" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="AT7" s="18">
+      <c r="AS7" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="AT7" s="20">
         <v>0.3854166666666667</v>
       </c>
-      <c r="AU7" s="13">
+      <c r="AU7" s="14">
         <v>-14.0</v>
       </c>
-      <c r="AV7" s="13">
+      <c r="AV7" s="14">
         <v>88.5</v>
       </c>
-      <c r="AW7" s="13">
+      <c r="AW7" s="14">
         <v>135.0</v>
       </c>
-      <c r="AX7" s="13">
+      <c r="AX7" s="14">
         <v>-46.5</v>
       </c>
-      <c r="AZ7" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="BA7" s="14" t="s">
-        <v>175</v>
+      <c r="AZ7" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="BA7" s="15" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <v>3.0</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F8" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G8" s="18">
+      <c r="D8" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G8" s="20">
         <v>0.8270833333333333</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="14">
         <v>11.0</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="14">
         <v>4.0</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="14">
         <v>6.0</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="18">
         <v>0.667</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="14">
         <v>4.0</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="14">
         <v>6.0</v>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="18">
         <v>0.667</v>
       </c>
-      <c r="O8" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P8" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Q8" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R8" s="13">
+      <c r="O8" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P8" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q8" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R8" s="14">
         <v>3.0</v>
       </c>
-      <c r="S8" s="13">
+      <c r="S8" s="14">
         <v>4.0</v>
       </c>
-      <c r="T8" s="17">
+      <c r="T8" s="18">
         <v>0.75</v>
       </c>
-      <c r="U8" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V8" s="13">
+      <c r="U8" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V8" s="14">
         <v>3.0</v>
       </c>
-      <c r="W8" s="13">
+      <c r="W8" s="14">
         <v>3.0</v>
       </c>
-      <c r="X8" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="Y8" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="Z8" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA8" s="13">
+      <c r="X8" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="Y8" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="Z8" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA8" s="14">
         <v>3.0</v>
       </c>
-      <c r="AB8" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AC8" s="13">
+      <c r="AB8" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AC8" s="14">
         <v>10.0</v>
       </c>
-      <c r="AD8" s="13">
+      <c r="AD8" s="14">
         <v>-4.0</v>
       </c>
-      <c r="AE8" s="17">
+      <c r="AE8" s="18">
         <v>0.667</v>
       </c>
-      <c r="AF8" s="17">
+      <c r="AF8" s="18">
         <v>0.709</v>
       </c>
-      <c r="AG8" s="13">
+      <c r="AG8" s="14">
         <v>0.67</v>
       </c>
-      <c r="AH8" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="AI8" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="AK8" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL8" s="18">
+      <c r="AH8" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="AI8" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="AK8" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="AL8" s="20">
         <v>0.8270833333333333</v>
       </c>
-      <c r="AM8" s="13">
+      <c r="AM8" s="14">
         <v>101.0</v>
       </c>
-      <c r="AN8" s="13">
+      <c r="AN8" s="14">
         <v>122.0</v>
       </c>
-      <c r="AO8" s="13">
+      <c r="AO8" s="14">
         <v>-21.0</v>
       </c>
-      <c r="AP8" s="13">
+      <c r="AP8" s="14">
         <v>-24.5</v>
       </c>
-      <c r="AQ8" s="13">
+      <c r="AQ8" s="14">
         <v>3.5</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="B9" s="14" t="s">
+      <c r="A9" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F9" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G9" s="18">
+      <c r="E9" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G9" s="20">
         <v>0.5215277777777778</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="14">
         <v>9.0</v>
       </c>
-      <c r="I9" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="J9" s="13">
+      <c r="I9" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="J9" s="14">
         <v>4.0</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="18">
         <v>0.5</v>
       </c>
-      <c r="L9" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="M9" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="N9" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="O9" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P9" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="Q9" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R9" s="13">
+      <c r="L9" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M9" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="N9" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="O9" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P9" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="Q9" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R9" s="14">
         <v>5.0</v>
       </c>
-      <c r="S9" s="13">
+      <c r="S9" s="14">
         <v>5.0</v>
       </c>
-      <c r="T9" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="U9" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V9" s="13">
+      <c r="T9" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="U9" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V9" s="14">
         <v>4.0</v>
       </c>
-      <c r="W9" s="13">
+      <c r="W9" s="14">
         <v>4.0</v>
       </c>
-      <c r="X9" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="Y9" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Z9" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AA9" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AB9" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AC9" s="13">
+      <c r="X9" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="Y9" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Z9" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AA9" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AB9" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AC9" s="14">
         <v>12.0</v>
       </c>
-      <c r="AD9" s="13">
+      <c r="AD9" s="14">
         <v>-6.0</v>
       </c>
-      <c r="AE9" s="17">
+      <c r="AE9" s="18">
         <v>0.5</v>
       </c>
-      <c r="AF9" s="17">
+      <c r="AF9" s="18">
         <v>0.726</v>
       </c>
-      <c r="AG9" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AH9" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="AI9" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="AK9" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL9" s="18">
+      <c r="AG9" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AH9" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="AI9" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="AK9" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="AL9" s="20">
         <v>0.5215277777777778</v>
       </c>
-      <c r="AM9" s="13">
+      <c r="AM9" s="14">
         <v>103.5</v>
       </c>
-      <c r="AN9" s="13">
+      <c r="AN9" s="14">
         <v>121.0</v>
       </c>
-      <c r="AO9" s="13">
+      <c r="AO9" s="14">
         <v>-17.5</v>
       </c>
-      <c r="AP9" s="13">
+      <c r="AP9" s="14">
         <v>-23.0</v>
       </c>
-      <c r="AQ9" s="13">
+      <c r="AQ9" s="14">
         <v>5.5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <v>17.0</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="14" t="s">
+      <c r="B10" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F10" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G10" s="18">
+      <c r="D10" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F10" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G10" s="20">
         <v>0.7777777777777778</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="14">
         <v>9.0</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="14">
         <v>3.0</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="14">
         <v>8.0</v>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="18">
         <v>0.375</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="14">
         <v>3.0</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="14">
         <v>6.0</v>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="18">
         <v>0.5</v>
       </c>
-      <c r="O10" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P10" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="Q10" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R10" s="13">
+      <c r="O10" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P10" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="Q10" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R10" s="14">
         <v>3.0</v>
       </c>
-      <c r="S10" s="13">
+      <c r="S10" s="14">
         <v>4.0</v>
       </c>
-      <c r="T10" s="17">
+      <c r="T10" s="18">
         <v>0.75</v>
       </c>
-      <c r="U10" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V10" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="W10" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="X10" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Y10" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z10" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA10" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AB10" s="13">
+      <c r="U10" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V10" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="W10" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="X10" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Y10" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z10" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA10" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AB10" s="14">
         <v>3.0</v>
       </c>
-      <c r="AC10" s="13">
+      <c r="AC10" s="14">
         <v>3.0</v>
       </c>
-      <c r="AD10" s="13">
+      <c r="AD10" s="14">
         <v>-12.0</v>
       </c>
-      <c r="AE10" s="17">
+      <c r="AE10" s="18">
         <v>0.375</v>
       </c>
-      <c r="AF10" s="17">
+      <c r="AF10" s="18">
         <v>0.461</v>
       </c>
-      <c r="AG10" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH10" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="AI10" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="AK10" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL10" s="18">
+      <c r="AG10" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH10" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="AI10" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="AK10" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="AL10" s="20">
         <v>0.6458333333333334</v>
       </c>
-      <c r="AM10" s="13">
+      <c r="AM10" s="14">
         <v>98.5</v>
       </c>
-      <c r="AN10" s="13">
+      <c r="AN10" s="14">
         <v>126.5</v>
       </c>
-      <c r="AO10" s="13">
+      <c r="AO10" s="14">
         <v>-28.0</v>
       </c>
-      <c r="AP10" s="13">
+      <c r="AP10" s="14">
         <v>-19.0</v>
       </c>
-      <c r="AQ10" s="13">
+      <c r="AQ10" s="14">
         <v>-9.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13">
+      <c r="A11" s="14">
         <v>7.0</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="14" t="s">
+      <c r="B11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="F11" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G11" s="18">
+      <c r="D11" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="F11" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G11" s="20">
         <v>0.6458333333333334</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="14">
         <v>9.0</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="14">
         <v>4.0</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="14">
         <v>6.0</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="18">
         <v>0.667</v>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="14">
         <v>4.0</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="14">
         <v>6.0</v>
       </c>
-      <c r="N11" s="17">
+      <c r="N11" s="18">
         <v>0.667</v>
       </c>
-      <c r="O11" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P11" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Q11" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R11" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="S11" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="T11" s="17">
+      <c r="O11" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P11" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q11" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R11" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="S11" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="T11" s="18">
         <v>0.5</v>
       </c>
-      <c r="U11" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V11" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="W11" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="X11" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="Y11" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Z11" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA11" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AB11" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AC11" s="13">
+      <c r="U11" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V11" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="W11" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="X11" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="Y11" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Z11" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA11" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AB11" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AC11" s="14">
         <v>7.0</v>
       </c>
-      <c r="AD11" s="13">
+      <c r="AD11" s="14">
         <v>-16.0</v>
       </c>
-      <c r="AE11" s="17">
+      <c r="AE11" s="18">
         <v>0.667</v>
       </c>
-      <c r="AF11" s="17">
+      <c r="AF11" s="18">
         <v>0.654</v>
       </c>
-      <c r="AG11" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AH11" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="AI11" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="AK11" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="AL11" s="18">
+      <c r="AG11" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AH11" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI11" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK11" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="AL11" s="20">
         <v>0.9861111111111112</v>
       </c>
-      <c r="AM11" s="13">
+      <c r="AM11" s="14">
         <v>96.0</v>
       </c>
-      <c r="AN11" s="13">
+      <c r="AN11" s="14">
         <v>128.5</v>
       </c>
-      <c r="AO11" s="13">
+      <c r="AO11" s="14">
         <v>-32.5</v>
       </c>
-      <c r="AP11" s="13">
+      <c r="AP11" s="14">
         <v>-15.0</v>
       </c>
-      <c r="AQ11" s="13">
+      <c r="AQ11" s="14">
         <v>-17.5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <v>42.0</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="F12" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G12" s="18">
+      <c r="E12" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="F12" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G12" s="20">
         <v>0.6048611111111111</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="14">
         <v>5.0</v>
       </c>
-      <c r="I12" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="J12" s="13">
+      <c r="I12" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="J12" s="14">
         <v>9.0</v>
       </c>
-      <c r="K12" s="17">
+      <c r="K12" s="18">
         <v>0.222</v>
       </c>
-      <c r="L12" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="M12" s="13">
+      <c r="L12" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M12" s="14">
         <v>3.0</v>
       </c>
-      <c r="N12" s="17">
+      <c r="N12" s="18">
         <v>0.333</v>
       </c>
-      <c r="O12" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="P12" s="13">
+      <c r="O12" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="P12" s="14">
         <v>6.0</v>
       </c>
-      <c r="Q12" s="17">
+      <c r="Q12" s="18">
         <v>0.167</v>
       </c>
-      <c r="R12" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S12" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="T12" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U12" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V12" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="W12" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="X12" s="13">
+      <c r="R12" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S12" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="T12" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U12" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V12" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="W12" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="X12" s="14">
         <v>3.0</v>
       </c>
-      <c r="Y12" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Z12" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA12" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AB12" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AC12" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AD12" s="13">
+      <c r="Y12" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Z12" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA12" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AB12" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AC12" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AD12" s="14">
         <v>-11.0</v>
       </c>
-      <c r="AE12" s="17">
+      <c r="AE12" s="18">
         <v>0.278</v>
       </c>
-      <c r="AF12" s="17">
+      <c r="AF12" s="18">
         <v>0.278</v>
       </c>
-      <c r="AG12" s="13">
+      <c r="AG12" s="14">
         <v>3.0</v>
       </c>
-      <c r="AH12" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="AI12" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="AK12" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="AL12" s="18">
+      <c r="AH12" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI12" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="AK12" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="AL12" s="20">
         <v>0.6048611111111111</v>
       </c>
-      <c r="AM12" s="13">
+      <c r="AM12" s="14">
         <v>95.5</v>
       </c>
-      <c r="AN12" s="13">
+      <c r="AN12" s="14">
         <v>129.0</v>
       </c>
-      <c r="AO12" s="13">
+      <c r="AO12" s="14">
         <v>-33.5</v>
       </c>
-      <c r="AP12" s="13">
+      <c r="AP12" s="14">
         <v>-14.2</v>
       </c>
-      <c r="AQ12" s="13">
+      <c r="AQ12" s="14">
         <v>-19.3</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13">
+      <c r="A13" s="14">
         <v>8.0</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="14" t="s">
+      <c r="B13" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="F13" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G13" s="18">
+      <c r="D13" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="F13" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G13" s="20">
         <v>0.9222222222222223</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="14">
         <v>5.0</v>
       </c>
-      <c r="I13" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="J13" s="13">
+      <c r="I13" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="J13" s="14">
         <v>3.0</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K13" s="18">
         <v>0.667</v>
       </c>
-      <c r="L13" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="M13" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="N13" s="17">
+      <c r="L13" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M13" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="N13" s="18">
         <v>0.5</v>
       </c>
-      <c r="O13" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="P13" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Q13" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="R13" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S13" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="T13" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U13" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V13" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="W13" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="X13" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Y13" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z13" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA13" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AB13" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AC13" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AD13" s="13">
+      <c r="O13" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="P13" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Q13" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="R13" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S13" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="T13" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U13" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V13" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="W13" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="X13" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Y13" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z13" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA13" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AB13" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AC13" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AD13" s="14">
         <v>-10.0</v>
       </c>
-      <c r="AE13" s="17">
+      <c r="AE13" s="18">
         <v>0.833</v>
       </c>
-      <c r="AF13" s="17">
+      <c r="AF13" s="18">
         <v>0.727</v>
       </c>
-      <c r="AG13" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH13" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AI13" s="14" t="s">
-        <v>206</v>
+      <c r="AG13" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH13" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="AI13" s="15" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13">
+      <c r="A14" s="14">
         <v>32.0</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="14" t="s">
+      <c r="B14" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F14" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G14" s="18">
+      <c r="F14" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G14" s="20">
         <v>0.9861111111111112</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="14">
         <v>4.0</v>
       </c>
-      <c r="I14" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="J14" s="13">
+      <c r="I14" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="J14" s="14">
         <v>9.0</v>
       </c>
-      <c r="K14" s="17">
+      <c r="K14" s="18">
         <v>0.111</v>
       </c>
-      <c r="L14" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="M14" s="13">
+      <c r="L14" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M14" s="14">
         <v>5.0</v>
       </c>
-      <c r="N14" s="17">
+      <c r="N14" s="18">
         <v>0.2</v>
       </c>
-      <c r="O14" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P14" s="13">
+      <c r="O14" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P14" s="14">
         <v>4.0</v>
       </c>
-      <c r="Q14" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R14" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="S14" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="T14" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="U14" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="V14" s="13">
+      <c r="Q14" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R14" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="S14" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="T14" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="U14" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="V14" s="14">
         <v>10.0</v>
       </c>
-      <c r="W14" s="13">
+      <c r="W14" s="14">
         <v>12.0</v>
       </c>
-      <c r="X14" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="Y14" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z14" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA14" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AB14" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AC14" s="13">
+      <c r="X14" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="Y14" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z14" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA14" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AB14" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AC14" s="14">
         <v>9.0</v>
       </c>
-      <c r="AD14" s="13">
+      <c r="AD14" s="14">
         <v>-15.0</v>
       </c>
-      <c r="AE14" s="17">
+      <c r="AE14" s="18">
         <v>0.111</v>
       </c>
-      <c r="AF14" s="17">
+      <c r="AF14" s="18">
         <v>0.202</v>
       </c>
-      <c r="AG14" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AH14" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="AI14" s="14" t="s">
-        <v>208</v>
+      <c r="AG14" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AH14" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="AI14" s="15" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13">
+      <c r="A15" s="14">
         <v>41.0</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="14" t="s">
+      <c r="B15" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="F15" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G15" s="18">
+      <c r="D15" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G15" s="20">
         <v>0.5555555555555556</v>
       </c>
-      <c r="H15" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="I15" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="J15" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="K15" s="17">
+      <c r="H15" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="I15" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="J15" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="K15" s="18">
         <v>0.5</v>
       </c>
-      <c r="L15" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="M15" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="N15" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="O15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P15" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Q15" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="T15" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="W15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="X15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Y15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AB15" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AC15" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AD15" s="13">
+      <c r="L15" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M15" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="N15" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="O15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P15" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Q15" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="T15" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="W15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="X15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Y15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AB15" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AC15" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AD15" s="14">
         <v>-5.0</v>
       </c>
-      <c r="AE15" s="17">
+      <c r="AE15" s="18">
         <v>0.5</v>
       </c>
-      <c r="AF15" s="17">
+      <c r="AF15" s="18">
         <v>0.5</v>
       </c>
-      <c r="AG15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH15" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="AI15" s="14" t="s">
-        <v>211</v>
+      <c r="AG15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH15" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="AI15" s="15" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13">
+      <c r="A16" s="14">
         <v>14.0</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="14" t="s">
+      <c r="B16" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F16" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G16" s="18">
+      <c r="F16" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G16" s="20">
         <v>0.2847222222222222</v>
       </c>
-      <c r="H16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J16" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="K16" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="L16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="M16" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="N16" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="O16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P16" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Q16" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="T16" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V16" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="W16" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="X16" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Y16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AB16" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AC16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AD16" s="13">
+      <c r="H16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="J16" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="K16" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="M16" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="N16" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P16" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Q16" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="T16" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V16" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="W16" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="X16" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Y16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AB16" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AC16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AD16" s="14">
         <v>-4.0</v>
       </c>
-      <c r="AE16" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AF16" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AG16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH16" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="AI16" s="14" t="s">
-        <v>213</v>
+      <c r="AE16" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AF16" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AG16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH16" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="AI16" s="15" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13">
+      <c r="A17" s="14">
         <v>28.0</v>
       </c>
-      <c r="B17" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" s="14" t="s">
+      <c r="B17" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="F17" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G17" s="18">
+      <c r="D17" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="F17" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G17" s="20">
         <v>0.5416666666666666</v>
       </c>
-      <c r="H17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J17" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="K17" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="L17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="M17" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="N17" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="O17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Q17" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="T17" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U17" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="V17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="W17" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="X17" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Y17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA17" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AB17" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AC17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AD17" s="13">
+      <c r="H17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="J17" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="K17" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="M17" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="N17" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q17" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="T17" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U17" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="V17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="W17" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="X17" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Y17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA17" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AB17" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AC17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AD17" s="14">
         <v>-6.0</v>
       </c>
-      <c r="AE17" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AF17" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AG17" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AH17" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="AI17" s="14" t="s">
-        <v>215</v>
+      <c r="AE17" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AF17" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AG17" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AH17" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="AI17" s="15" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13">
+      <c r="A18" s="14">
         <v>6.0</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C18" s="14" t="s">
+      <c r="B18" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" s="14" t="s">
+      <c r="D18" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="H18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="M18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="N18" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="O18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Q18" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="T18" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="W18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="X18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Y18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AB18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AC18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AD18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AE18" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AF18" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AG18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI18" s="14" t="s">
-        <v>187</v>
+      <c r="F18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="G18" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="J18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="K18" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="M18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q18" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="T18" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="W18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="X18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Y18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AB18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AC18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AD18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AE18" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AF18" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AG18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH18" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI18" s="15" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" s="14" t="s">
+      <c r="A19" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="H19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="M19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="N19" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="O19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Q19" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="T19" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="W19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="X19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Y19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AB19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AC19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AD19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AE19" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AF19" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AG19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH19" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI19" s="14" t="s">
-        <v>191</v>
+      <c r="D19" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="G19" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="J19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="K19" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="M19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q19" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="T19" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="W19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="X19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Y19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AB19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AC19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AD19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AE19" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AF19" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AG19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH19" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI19" s="15" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13">
+      <c r="A20" s="14">
         <v>25.0</v>
       </c>
-      <c r="B20" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" s="14" t="s">
+      <c r="B20" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="H20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="K20" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="L20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="M20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="N20" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="O20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Q20" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="T20" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="W20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="X20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Y20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AB20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AC20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AD20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AE20" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AF20" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AG20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH20" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI20" s="14" t="s">
-        <v>196</v>
+      <c r="E20" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="G20" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="I20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="K20" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="M20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q20" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="T20" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="W20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="X20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Y20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AB20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AC20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AD20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AE20" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AF20" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AG20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH20" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI20" s="15" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F21" s="13">
+      <c r="A21" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="F21" s="14">
         <v>1.0</v>
       </c>
       <c r="G21" s="16">
         <v>10.0</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="14">
         <v>110.0</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="14">
         <v>40.0</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="14">
         <v>83.0</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="18">
         <v>0.482</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="14">
         <v>36.0</v>
       </c>
-      <c r="M21" s="13">
+      <c r="M21" s="14">
         <v>61.0</v>
       </c>
-      <c r="N21" s="17">
+      <c r="N21" s="18">
         <v>0.59</v>
       </c>
-      <c r="O21" s="13">
+      <c r="O21" s="14">
         <v>4.0</v>
       </c>
-      <c r="P21" s="13">
+      <c r="P21" s="14">
         <v>22.0</v>
       </c>
-      <c r="Q21" s="17">
+      <c r="Q21" s="18">
         <v>0.182</v>
       </c>
-      <c r="R21" s="13">
+      <c r="R21" s="14">
         <v>26.0</v>
       </c>
-      <c r="S21" s="13">
+      <c r="S21" s="14">
         <v>34.0</v>
       </c>
-      <c r="T21" s="17">
+      <c r="T21" s="18">
         <v>0.765</v>
       </c>
-      <c r="U21" s="13">
+      <c r="U21" s="14">
         <v>11.0</v>
       </c>
-      <c r="V21" s="13">
+      <c r="V21" s="14">
         <v>33.0</v>
       </c>
-      <c r="W21" s="13">
+      <c r="W21" s="14">
         <v>44.0</v>
       </c>
-      <c r="X21" s="13">
+      <c r="X21" s="14">
         <v>17.0</v>
       </c>
-      <c r="Y21" s="13">
+      <c r="Y21" s="14">
         <v>7.0</v>
       </c>
-      <c r="Z21" s="13">
+      <c r="Z21" s="14">
         <v>5.0</v>
       </c>
-      <c r="AA21" s="13">
+      <c r="AA21" s="14">
         <v>19.0</v>
       </c>
-      <c r="AB21" s="13">
+      <c r="AB21" s="14">
         <v>26.0</v>
       </c>
-      <c r="AC21" s="13">
+      <c r="AC21" s="14">
         <v>102.0</v>
       </c>
-      <c r="AD21" s="13">
+      <c r="AD21" s="14">
         <v>-24.0</v>
       </c>
-      <c r="AE21" s="17">
+      <c r="AE21" s="18">
         <v>0.506</v>
       </c>
-      <c r="AF21" s="17">
+      <c r="AF21" s="18">
         <v>0.561</v>
       </c>
-      <c r="AG21" s="13">
+      <c r="AG21" s="14">
         <v>0.89</v>
       </c>
-      <c r="AH21" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="AI21" s="14" t="s">
-        <v>219</v>
+      <c r="AH21" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="AI21" s="15" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -7654,12 +7654,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
@@ -7670,22 +7670,22 @@
         <v>3</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>9</v>
@@ -7697,13 +7697,13 @@
         <v>11</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="O4" s="7" t="s">
         <v>12</v>
@@ -7721,93 +7721,93 @@
         <v>16</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="W4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="X4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y4" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="7" t="s">
+      <c r="Z4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="W4" s="7" t="s">
+      <c r="AA4" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="X4" s="7" t="s">
+      <c r="AB4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="Y4" s="7" t="s">
+      <c r="AC4" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="Z4" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA4" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB4" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD4" s="9" t="s">
-        <v>69</v>
+      <c r="AD4" s="10" t="s">
+        <v>87</v>
       </c>
       <c r="AE4" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF4" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG4" s="7" t="s">
         <v>27</v>
       </c>
       <c r="AH4" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="AI4" s="7" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="AJ4" s="11"/>
       <c r="AK4" s="7" t="s">
         <v>3</v>
       </c>
       <c r="AL4" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM4" s="7" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AN4" s="7" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="AO4" s="7" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AP4" s="7" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="AQ4" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT4" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="AR4" s="11"/>
-      <c r="AS4" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="AT4" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="AU4" s="12" t="str">
+      <c r="AU4" s="13" t="str">
         <v>#ERROR!</v>
       </c>
       <c r="AV4" s="7" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AW4" s="7" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="AX4" s="7" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AY4" s="11"/>
       <c r="AZ4" s="7" t="s">
@@ -7818,2062 +7818,2062 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13">
+      <c r="A5" s="14">
         <v>13.0</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F5" s="13">
+      <c r="E5" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="14">
         <v>1.0</v>
       </c>
       <c r="G5" s="16">
         <v>1.4520833333333334</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="14">
         <v>19.0</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="14">
         <v>6.0</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="14">
         <v>14.0</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="18">
         <v>0.429</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="14">
         <v>4.0</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="14">
         <v>8.0</v>
       </c>
-      <c r="N5" s="17">
+      <c r="N5" s="18">
         <v>0.5</v>
       </c>
-      <c r="O5" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="P5" s="13">
+      <c r="O5" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="P5" s="14">
         <v>6.0</v>
       </c>
-      <c r="Q5" s="17">
+      <c r="Q5" s="18">
         <v>0.333</v>
       </c>
-      <c r="R5" s="13">
+      <c r="R5" s="14">
         <v>5.0</v>
       </c>
-      <c r="S5" s="13">
+      <c r="S5" s="14">
         <v>5.0</v>
       </c>
-      <c r="T5" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="U5" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V5" s="13">
+      <c r="T5" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="U5" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V5" s="14">
         <v>5.0</v>
       </c>
-      <c r="W5" s="13">
+      <c r="W5" s="14">
         <v>5.0</v>
       </c>
-      <c r="X5" s="13">
+      <c r="X5" s="14">
         <v>3.0</v>
       </c>
-      <c r="Y5" s="13">
+      <c r="Y5" s="14">
         <v>3.0</v>
       </c>
-      <c r="Z5" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA5" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AB5" s="13">
+      <c r="Z5" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA5" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AB5" s="14">
         <v>4.0</v>
       </c>
-      <c r="AC5" s="13">
+      <c r="AC5" s="14">
         <v>20.0</v>
       </c>
-      <c r="AD5" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AE5" s="17">
+      <c r="AD5" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AE5" s="18">
         <v>0.5</v>
       </c>
-      <c r="AF5" s="17">
+      <c r="AF5" s="18">
         <v>0.586</v>
       </c>
-      <c r="AG5" s="13">
+      <c r="AG5" s="14">
         <v>1.5</v>
       </c>
-      <c r="AH5" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="AI5" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="AK5" s="14" t="s">
-        <v>108</v>
+      <c r="AH5" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI5" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="AK5" s="15" t="s">
+        <v>125</v>
       </c>
       <c r="AL5" s="16">
         <v>1.1319444444444444</v>
       </c>
-      <c r="AM5" s="13">
+      <c r="AM5" s="14">
         <v>105.0</v>
       </c>
-      <c r="AN5" s="13">
+      <c r="AN5" s="14">
         <v>96.0</v>
       </c>
-      <c r="AO5" s="13">
+      <c r="AO5" s="14">
         <v>9.0</v>
       </c>
-      <c r="AP5" s="13">
+      <c r="AP5" s="14">
         <v>-14.2</v>
       </c>
-      <c r="AQ5" s="13">
+      <c r="AQ5" s="14">
         <v>23.2</v>
       </c>
-      <c r="AS5" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="AT5" s="18">
+      <c r="AS5" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="AT5" s="20">
         <v>0.5555555555555556</v>
       </c>
-      <c r="AU5" s="13">
+      <c r="AU5" s="14">
         <v>8.0</v>
       </c>
-      <c r="AV5" s="13">
+      <c r="AV5" s="14">
         <v>112.5</v>
       </c>
-      <c r="AW5" s="13">
+      <c r="AW5" s="14">
         <v>98.0</v>
       </c>
-      <c r="AX5" s="13">
+      <c r="AX5" s="14">
         <v>14.5</v>
       </c>
-      <c r="AZ5" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="BA5" s="14" t="s">
-        <v>114</v>
+      <c r="AZ5" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="BA5" s="15" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <v>33.0</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <v>1.0</v>
       </c>
       <c r="G6" s="16">
         <v>1.2861111111111112</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="14">
         <v>19.0</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="14">
         <v>7.0</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="14">
         <v>12.0</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="18">
         <v>0.583</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="14">
         <v>7.0</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="14">
         <v>12.0</v>
       </c>
-      <c r="N6" s="17">
+      <c r="N6" s="18">
         <v>0.583</v>
       </c>
-      <c r="O6" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P6" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Q6" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R6" s="13">
+      <c r="O6" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P6" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q6" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R6" s="14">
         <v>5.0</v>
       </c>
-      <c r="S6" s="13">
+      <c r="S6" s="14">
         <v>7.0</v>
       </c>
-      <c r="T6" s="17">
+      <c r="T6" s="18">
         <v>0.714</v>
       </c>
-      <c r="U6" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="V6" s="13">
+      <c r="U6" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="V6" s="14">
         <v>6.0</v>
       </c>
-      <c r="W6" s="13">
+      <c r="W6" s="14">
         <v>8.0</v>
       </c>
-      <c r="X6" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="Y6" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Z6" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA6" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AB6" s="13">
+      <c r="X6" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Z6" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA6" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AB6" s="14">
         <v>5.0</v>
       </c>
-      <c r="AC6" s="13">
+      <c r="AC6" s="14">
         <v>21.0</v>
       </c>
-      <c r="AD6" s="13">
+      <c r="AD6" s="14">
         <v>5.0</v>
       </c>
-      <c r="AE6" s="17">
+      <c r="AE6" s="18">
         <v>0.583</v>
       </c>
-      <c r="AF6" s="17">
+      <c r="AF6" s="18">
         <v>0.63</v>
       </c>
-      <c r="AG6" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AH6" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="AI6" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="AK6" s="14" t="s">
-        <v>118</v>
+      <c r="AG6" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AH6" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI6" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="AK6" s="15" t="s">
+        <v>119</v>
       </c>
       <c r="AL6" s="16">
         <v>1.2861111111111112</v>
       </c>
-      <c r="AM6" s="13">
+      <c r="AM6" s="14">
         <v>102.8</v>
       </c>
-      <c r="AN6" s="13">
+      <c r="AN6" s="14">
         <v>98.5</v>
       </c>
-      <c r="AO6" s="13">
+      <c r="AO6" s="14">
         <v>4.3</v>
       </c>
-      <c r="AP6" s="13">
+      <c r="AP6" s="14">
         <v>-11.5</v>
       </c>
-      <c r="AQ6" s="13">
+      <c r="AQ6" s="14">
         <v>15.8</v>
       </c>
-      <c r="AS6" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="AT6" s="18">
+      <c r="AS6" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="AT6" s="20">
         <v>0.28125</v>
       </c>
-      <c r="AU6" s="13">
+      <c r="AU6" s="14">
         <v>4.0</v>
       </c>
-      <c r="AV6" s="13">
+      <c r="AV6" s="14">
         <v>115.0</v>
       </c>
-      <c r="AW6" s="13">
+      <c r="AW6" s="14">
         <v>102.0</v>
       </c>
-      <c r="AX6" s="13">
+      <c r="AX6" s="14">
         <v>13.0</v>
       </c>
-      <c r="AZ6" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="BA6" s="14" t="s">
-        <v>121</v>
+      <c r="AZ6" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="BA6" s="15" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="B7" s="14" t="s">
+      <c r="A7" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F7" s="13">
+      <c r="E7" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F7" s="14">
         <v>1.0</v>
       </c>
       <c r="G7" s="16">
         <v>1.1868055555555554</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="14">
         <v>17.0</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="14">
         <v>6.0</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="14">
         <v>10.0</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="18">
         <v>0.6</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="14">
         <v>4.0</v>
       </c>
-      <c r="M7" s="13">
+      <c r="M7" s="14">
         <v>7.0</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="18">
         <v>0.571</v>
       </c>
-      <c r="O7" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="P7" s="13">
+      <c r="O7" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="P7" s="14">
         <v>3.0</v>
       </c>
-      <c r="Q7" s="17">
+      <c r="Q7" s="18">
         <v>0.667</v>
       </c>
-      <c r="R7" s="13">
+      <c r="R7" s="14">
         <v>3.0</v>
       </c>
-      <c r="S7" s="13">
+      <c r="S7" s="14">
         <v>3.0</v>
       </c>
-      <c r="T7" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="U7" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="V7" s="13">
+      <c r="T7" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="U7" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="V7" s="14">
         <v>7.0</v>
       </c>
-      <c r="W7" s="13">
+      <c r="W7" s="14">
         <v>8.0</v>
       </c>
-      <c r="X7" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="Y7" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Z7" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AA7" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AB7" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AC7" s="13">
+      <c r="X7" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Z7" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AA7" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AB7" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AC7" s="14">
         <v>24.0</v>
       </c>
-      <c r="AD7" s="13">
+      <c r="AD7" s="14">
         <v>-4.0</v>
       </c>
-      <c r="AE7" s="17">
+      <c r="AE7" s="18">
         <v>0.7</v>
       </c>
-      <c r="AF7" s="17">
+      <c r="AF7" s="18">
         <v>0.751</v>
       </c>
-      <c r="AG7" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AH7" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="AI7" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="AK7" s="14" t="s">
-        <v>112</v>
+      <c r="AG7" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AH7" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI7" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AK7" s="15" t="s">
+        <v>101</v>
       </c>
       <c r="AL7" s="16">
         <v>1.4520833333333334</v>
       </c>
-      <c r="AM7" s="13">
+      <c r="AM7" s="14">
         <v>101.5</v>
       </c>
-      <c r="AN7" s="13">
+      <c r="AN7" s="14">
         <v>100.2</v>
       </c>
-      <c r="AO7" s="13">
+      <c r="AO7" s="14">
         <v>1.3</v>
       </c>
-      <c r="AP7" s="13">
+      <c r="AP7" s="14">
         <v>-8.0</v>
       </c>
-      <c r="AQ7" s="13">
+      <c r="AQ7" s="14">
         <v>9.3</v>
       </c>
-      <c r="AS7" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="AT7" s="18">
+      <c r="AS7" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="AT7" s="20">
         <v>0.3541666666666667</v>
       </c>
-      <c r="AU7" s="13">
+      <c r="AU7" s="14">
         <v>-11.0</v>
       </c>
-      <c r="AV7" s="13">
+      <c r="AV7" s="14">
         <v>88.0</v>
       </c>
-      <c r="AW7" s="13">
+      <c r="AW7" s="14">
         <v>114.5</v>
       </c>
-      <c r="AX7" s="13">
+      <c r="AX7" s="14">
         <v>-26.5</v>
       </c>
-      <c r="AZ7" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="BA7" s="14" t="s">
-        <v>127</v>
+      <c r="AZ7" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="BA7" s="15" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <v>17.0</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F8" s="13">
+      <c r="D8" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="14">
         <v>1.0</v>
       </c>
       <c r="G8" s="16">
         <v>1.2916666666666667</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="14">
         <v>15.0</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="14">
         <v>6.0</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="14">
         <v>11.0</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="18">
         <v>0.545</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="14">
         <v>4.0</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="14">
         <v>8.0</v>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="18">
         <v>0.5</v>
       </c>
-      <c r="O8" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="P8" s="13">
+      <c r="O8" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="P8" s="14">
         <v>3.0</v>
       </c>
-      <c r="Q8" s="17">
+      <c r="Q8" s="18">
         <v>0.667</v>
       </c>
-      <c r="R8" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="S8" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="T8" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="U8" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="V8" s="13">
+      <c r="R8" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="S8" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="T8" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="U8" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="V8" s="14">
         <v>4.0</v>
       </c>
-      <c r="W8" s="13">
+      <c r="W8" s="14">
         <v>6.0</v>
       </c>
-      <c r="X8" s="13">
+      <c r="X8" s="14">
         <v>3.0</v>
       </c>
-      <c r="Y8" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z8" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA8" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AB8" s="13">
+      <c r="Y8" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z8" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA8" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AB8" s="14">
         <v>3.0</v>
       </c>
-      <c r="AC8" s="13">
+      <c r="AC8" s="14">
         <v>19.0</v>
       </c>
-      <c r="AD8" s="13">
+      <c r="AD8" s="14">
         <v>-6.0</v>
       </c>
-      <c r="AE8" s="17">
+      <c r="AE8" s="18">
         <v>0.636</v>
       </c>
-      <c r="AF8" s="17">
+      <c r="AF8" s="18">
         <v>0.656</v>
       </c>
-      <c r="AG8" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH8" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="AI8" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="AK8" s="14" t="s">
-        <v>132</v>
+      <c r="AG8" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH8" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI8" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="AK8" s="15" t="s">
+        <v>129</v>
       </c>
       <c r="AL8" s="16">
         <v>1.1868055555555554</v>
       </c>
-      <c r="AM8" s="13">
+      <c r="AM8" s="14">
         <v>101.0</v>
       </c>
-      <c r="AN8" s="13">
+      <c r="AN8" s="14">
         <v>102.5</v>
       </c>
-      <c r="AO8" s="13">
+      <c r="AO8" s="14">
         <v>-1.5</v>
       </c>
-      <c r="AP8" s="13">
+      <c r="AP8" s="14">
         <v>-4.0</v>
       </c>
-      <c r="AQ8" s="13">
+      <c r="AQ8" s="14">
         <v>2.5</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13">
+      <c r="A9" s="14">
         <v>14.0</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="14" t="s">
+      <c r="B9" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F9" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G9" s="18">
+      <c r="F9" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G9" s="20">
         <v>0.4861111111111111</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="14">
         <v>9.0</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="14">
         <v>4.0</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="14">
         <v>6.0</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="18">
         <v>0.667</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="14">
         <v>3.0</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="14">
         <v>4.0</v>
       </c>
-      <c r="N9" s="17">
+      <c r="N9" s="18">
         <v>0.75</v>
       </c>
-      <c r="O9" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="P9" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="Q9" s="17">
+      <c r="O9" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="P9" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="Q9" s="18">
         <v>0.5</v>
       </c>
-      <c r="R9" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S9" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="T9" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U9" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V9" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="W9" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="X9" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="Y9" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Z9" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA9" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AB9" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AC9" s="13">
+      <c r="R9" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S9" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="T9" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U9" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V9" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="W9" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="X9" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="Y9" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Z9" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA9" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AB9" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AC9" s="14">
         <v>10.0</v>
       </c>
-      <c r="AD9" s="13">
+      <c r="AD9" s="14">
         <v>3.0</v>
       </c>
-      <c r="AE9" s="17">
+      <c r="AE9" s="18">
         <v>0.75</v>
       </c>
-      <c r="AF9" s="17">
+      <c r="AF9" s="18">
         <v>0.75</v>
       </c>
-      <c r="AG9" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH9" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="AI9" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK9" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="AL9" s="18">
+      <c r="AG9" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH9" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="AI9" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AK9" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="AL9" s="20">
         <v>0.4861111111111111</v>
       </c>
-      <c r="AM9" s="13">
+      <c r="AM9" s="14">
         <v>105.0</v>
       </c>
-      <c r="AN9" s="13">
+      <c r="AN9" s="14">
         <v>99.5</v>
       </c>
-      <c r="AO9" s="13">
+      <c r="AO9" s="14">
         <v>5.5</v>
       </c>
-      <c r="AP9" s="13">
+      <c r="AP9" s="14">
         <v>-2.0</v>
       </c>
-      <c r="AQ9" s="13">
+      <c r="AQ9" s="14">
         <v>7.5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <v>35.0</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="14" t="s">
+      <c r="B10" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="F10" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G10" s="18">
+      <c r="D10" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G10" s="20">
         <v>0.7138888888888889</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="14">
         <v>9.0</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="14">
         <v>4.0</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="14">
         <v>4.0</v>
       </c>
-      <c r="K10" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="L10" s="13">
+      <c r="K10" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="L10" s="14">
         <v>4.0</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="14">
         <v>4.0</v>
       </c>
-      <c r="N10" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="O10" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P10" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Q10" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R10" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="S10" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="T10" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="U10" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="V10" s="13">
+      <c r="N10" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="O10" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P10" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q10" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R10" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="S10" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="T10" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="U10" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="V10" s="14">
         <v>5.0</v>
       </c>
-      <c r="W10" s="13">
+      <c r="W10" s="14">
         <v>6.0</v>
       </c>
-      <c r="X10" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Y10" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Z10" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AA10" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AB10" s="13">
+      <c r="X10" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Y10" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Z10" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AA10" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AB10" s="14">
         <v>3.0</v>
       </c>
-      <c r="AC10" s="13">
+      <c r="AC10" s="14">
         <v>15.0</v>
       </c>
-      <c r="AD10" s="13">
+      <c r="AD10" s="14">
         <v>-8.0</v>
       </c>
-      <c r="AE10" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="AF10" s="17">
+      <c r="AE10" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="AF10" s="18">
         <v>1.013</v>
       </c>
-      <c r="AG10" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH10" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="AI10" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="AK10" s="14" t="s">
-        <v>146</v>
+      <c r="AG10" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH10" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="AI10" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="AK10" s="15" t="s">
+        <v>186</v>
       </c>
       <c r="AL10" s="16">
         <v>1.2916666666666667</v>
       </c>
-      <c r="AM10" s="13">
+      <c r="AM10" s="14">
         <v>98.5</v>
       </c>
-      <c r="AN10" s="13">
+      <c r="AN10" s="14">
         <v>103.0</v>
       </c>
-      <c r="AO10" s="13">
+      <c r="AO10" s="14">
         <v>-4.5</v>
       </c>
-      <c r="AP10" s="13">
+      <c r="AP10" s="14">
         <v>0.5</v>
       </c>
-      <c r="AQ10" s="13">
+      <c r="AQ10" s="14">
         <v>-5.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13">
+      <c r="A11" s="14">
         <v>42.0</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="F11" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G11" s="18">
+      <c r="E11" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="F11" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G11" s="20">
         <v>0.9993055555555556</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="14">
         <v>7.0</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="14">
         <v>3.0</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="14">
         <v>8.0</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="18">
         <v>0.375</v>
       </c>
-      <c r="L11" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="M11" s="13">
+      <c r="L11" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M11" s="14">
         <v>6.0</v>
       </c>
-      <c r="N11" s="17">
+      <c r="N11" s="18">
         <v>0.333</v>
       </c>
-      <c r="O11" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="P11" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="Q11" s="17">
+      <c r="O11" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="P11" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="Q11" s="18">
         <v>0.5</v>
       </c>
-      <c r="R11" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S11" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="T11" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U11" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V11" s="13">
+      <c r="R11" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S11" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="T11" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U11" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V11" s="14">
         <v>3.0</v>
       </c>
-      <c r="W11" s="13">
+      <c r="W11" s="14">
         <v>3.0</v>
       </c>
-      <c r="X11" s="13">
+      <c r="X11" s="14">
         <v>3.0</v>
       </c>
-      <c r="Y11" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Z11" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA11" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AB11" s="13">
+      <c r="Y11" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Z11" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA11" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AB11" s="14">
         <v>3.0</v>
       </c>
-      <c r="AC11" s="13">
+      <c r="AC11" s="14">
         <v>8.0</v>
       </c>
-      <c r="AD11" s="13">
+      <c r="AD11" s="14">
         <v>-7.0</v>
       </c>
-      <c r="AE11" s="17">
+      <c r="AE11" s="18">
         <v>0.438</v>
       </c>
-      <c r="AF11" s="17">
+      <c r="AF11" s="18">
         <v>0.438</v>
       </c>
-      <c r="AG11" s="13">
+      <c r="AG11" s="14">
         <v>3.0</v>
       </c>
-      <c r="AH11" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="AI11" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="AK11" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL11" s="18">
+      <c r="AH11" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI11" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="AK11" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="AL11" s="20">
         <v>0.7138888888888889</v>
       </c>
-      <c r="AM11" s="13">
+      <c r="AM11" s="14">
         <v>96.0</v>
       </c>
-      <c r="AN11" s="13">
+      <c r="AN11" s="14">
         <v>106.5</v>
       </c>
-      <c r="AO11" s="13">
+      <c r="AO11" s="14">
         <v>-10.5</v>
       </c>
-      <c r="AP11" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AQ11" s="13">
+      <c r="AP11" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AQ11" s="14">
         <v>-12.5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <v>7.0</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="14" t="s">
+      <c r="B12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="F12" s="13">
+      <c r="D12" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="F12" s="14">
         <v>1.0</v>
       </c>
       <c r="G12" s="16">
         <v>1.1319444444444444</v>
       </c>
-      <c r="H12" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="I12" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J12" s="13">
+      <c r="H12" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="I12" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="14">
         <v>4.0</v>
       </c>
-      <c r="K12" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="L12" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="M12" s="13">
+      <c r="K12" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L12" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="M12" s="14">
         <v>4.0</v>
       </c>
-      <c r="N12" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="O12" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P12" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Q12" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R12" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="S12" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="T12" s="17">
+      <c r="N12" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P12" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q12" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R12" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="S12" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="T12" s="18">
         <v>0.5</v>
       </c>
-      <c r="U12" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="V12" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="W12" s="13">
+      <c r="U12" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="V12" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="W12" s="14">
         <v>3.0</v>
       </c>
-      <c r="X12" s="13">
+      <c r="X12" s="14">
         <v>5.0</v>
       </c>
-      <c r="Y12" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Z12" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA12" s="13">
+      <c r="Y12" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Z12" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA12" s="14">
         <v>3.0</v>
       </c>
-      <c r="AB12" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AC12" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AD12" s="13">
+      <c r="AB12" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AC12" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AD12" s="14">
         <v>12.0</v>
       </c>
-      <c r="AE12" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AF12" s="17">
+      <c r="AE12" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AF12" s="18">
         <v>0.102</v>
       </c>
-      <c r="AG12" s="13">
+      <c r="AG12" s="14">
         <v>1.67</v>
       </c>
-      <c r="AH12" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="AI12" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="AK12" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL12" s="18">
+      <c r="AH12" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="AI12" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="AK12" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="AL12" s="20">
         <v>0.6243055555555556</v>
       </c>
-      <c r="AM12" s="13">
+      <c r="AM12" s="14">
         <v>94.0</v>
       </c>
-      <c r="AN12" s="13">
+      <c r="AN12" s="14">
         <v>108.0</v>
       </c>
-      <c r="AO12" s="13">
+      <c r="AO12" s="14">
         <v>-14.0</v>
       </c>
-      <c r="AP12" s="13">
+      <c r="AP12" s="14">
         <v>3.5</v>
       </c>
-      <c r="AQ12" s="13">
+      <c r="AQ12" s="14">
         <v>-17.5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13">
+      <c r="A13" s="14">
         <v>3.0</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="14" t="s">
+      <c r="B13" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F13" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G13" s="18">
+      <c r="D13" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F13" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G13" s="20">
         <v>0.6243055555555556</v>
       </c>
-      <c r="H13" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="I13" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J13" s="13">
+      <c r="H13" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="I13" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="J13" s="14">
         <v>6.0</v>
       </c>
-      <c r="K13" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="L13" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="M13" s="13">
+      <c r="K13" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L13" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="M13" s="14">
         <v>3.0</v>
       </c>
-      <c r="N13" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="O13" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P13" s="13">
+      <c r="N13" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P13" s="14">
         <v>3.0</v>
       </c>
-      <c r="Q13" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R13" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="S13" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="T13" s="17">
+      <c r="Q13" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R13" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="S13" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="T13" s="18">
         <v>0.5</v>
       </c>
-      <c r="U13" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V13" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="W13" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="X13" s="13">
+      <c r="U13" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V13" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="W13" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="X13" s="14">
         <v>3.0</v>
       </c>
-      <c r="Y13" s="13">
+      <c r="Y13" s="14">
         <v>3.0</v>
       </c>
-      <c r="Z13" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA13" s="13">
+      <c r="Z13" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA13" s="14">
         <v>5.0</v>
       </c>
-      <c r="AB13" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AC13" s="13">
+      <c r="AB13" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AC13" s="14">
         <v>-4.0</v>
       </c>
-      <c r="AD13" s="13">
+      <c r="AD13" s="14">
         <v>-9.0</v>
       </c>
-      <c r="AE13" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AF13" s="17">
+      <c r="AE13" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AF13" s="18">
         <v>0.073</v>
       </c>
-      <c r="AG13" s="13">
+      <c r="AG13" s="14">
         <v>0.6</v>
       </c>
-      <c r="AH13" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="AI13" s="14" t="s">
-        <v>167</v>
+      <c r="AH13" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="AI13" s="15" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13">
+      <c r="A14" s="14">
         <v>8.0</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="14" t="s">
+      <c r="B14" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="F14" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G14" s="18">
+      <c r="D14" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="F14" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G14" s="20">
         <v>0.2722222222222222</v>
       </c>
-      <c r="H14" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I14" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J14" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="K14" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="L14" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="M14" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="N14" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="O14" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P14" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Q14" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R14" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S14" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="T14" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U14" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="V14" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="W14" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="X14" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Y14" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z14" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA14" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AB14" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AC14" s="13">
+      <c r="H14" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="J14" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="K14" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L14" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="M14" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="N14" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P14" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Q14" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R14" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S14" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="T14" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U14" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="V14" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="W14" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="X14" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Y14" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z14" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA14" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AB14" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AC14" s="14">
         <v>-1.0</v>
       </c>
-      <c r="AD14" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AE14" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AF14" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AG14" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH14" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="AI14" s="14" t="s">
-        <v>172</v>
+      <c r="AD14" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AE14" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AF14" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AG14" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH14" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="AI14" s="15" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13">
+      <c r="A15" s="14">
         <v>32.0</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="14" t="s">
+      <c r="B15" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F15" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="G15" s="18">
+      <c r="F15" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="G15" s="20">
         <v>0.5555555555555556</v>
       </c>
-      <c r="H15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J15" s="13">
+      <c r="H15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="I15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="J15" s="14">
         <v>7.0</v>
       </c>
-      <c r="K15" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="L15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="M15" s="13">
+      <c r="K15" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="M15" s="14">
         <v>4.0</v>
       </c>
-      <c r="N15" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="O15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P15" s="13">
+      <c r="N15" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P15" s="14">
         <v>3.0</v>
       </c>
-      <c r="Q15" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="T15" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U15" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="V15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="W15" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="X15" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Y15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA15" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AB15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AC15" s="13">
+      <c r="Q15" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="T15" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U15" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="V15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="W15" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="X15" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="Y15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA15" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AB15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AC15" s="14">
         <v>-6.0</v>
       </c>
-      <c r="AD15" s="13">
+      <c r="AD15" s="14">
         <v>-4.0</v>
       </c>
-      <c r="AE15" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AF15" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AG15" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AH15" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="AI15" s="14" t="s">
-        <v>177</v>
+      <c r="AE15" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AF15" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AG15" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="AH15" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="AI15" s="15" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13">
+      <c r="A16" s="14">
         <v>41.0</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="14" t="s">
+      <c r="B16" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="F16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="G16" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="H16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="L16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="M16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="N16" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="O16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Q16" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="T16" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="W16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="X16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Y16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AB16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AC16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AD16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AE16" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AF16" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AG16" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH16" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI16" s="14" t="s">
-        <v>181</v>
+      <c r="D16" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="J16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="K16" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="M16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q16" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="T16" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="W16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="X16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Y16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AB16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AC16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AD16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AE16" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AF16" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AG16" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH16" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI16" s="15" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13">
+      <c r="A17" s="14">
         <v>28.0</v>
       </c>
-      <c r="B17" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" s="14" t="s">
+      <c r="B17" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="F17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="G17" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="H17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="K17" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="L17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="M17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="N17" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="O17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Q17" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="T17" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="W17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="X17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Y17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AB17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AC17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AD17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AE17" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AF17" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AG17" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH17" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI17" s="14" t="s">
-        <v>181</v>
+      <c r="D17" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="G17" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="K17" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="M17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q17" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="T17" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="W17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="X17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Y17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AB17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AC17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AD17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AE17" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AF17" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AG17" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH17" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI17" s="15" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13">
+      <c r="A18" s="14">
         <v>6.0</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C18" s="14" t="s">
+      <c r="B18" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" s="14" t="s">
+      <c r="D18" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="H18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="M18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="N18" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="O18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Q18" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="T18" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="W18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="X18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Y18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AB18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AC18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AD18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AE18" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AF18" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AG18" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI18" s="14" t="s">
-        <v>187</v>
+      <c r="F18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="G18" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="J18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="K18" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="M18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q18" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="T18" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="W18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="X18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Y18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AB18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AC18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AD18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AE18" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AF18" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AG18" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH18" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI18" s="15" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" s="14" t="s">
+      <c r="A19" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="H19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="M19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="N19" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="O19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Q19" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="T19" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="W19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="X19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Y19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AB19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AC19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AD19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AE19" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AF19" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AG19" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH19" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI19" s="14" t="s">
-        <v>191</v>
+      <c r="D19" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="G19" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="J19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="K19" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="M19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q19" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="T19" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="W19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="X19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Y19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AB19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AC19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AD19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AE19" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AF19" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AG19" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH19" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI19" s="15" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13">
+      <c r="A20" s="14">
         <v>25.0</v>
       </c>
-      <c r="B20" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" s="14" t="s">
+      <c r="B20" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="H20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="K20" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="L20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="M20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="N20" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="O20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="P20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Q20" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="R20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="S20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="T20" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="U20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="V20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="W20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="X20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Y20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="Z20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AA20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AB20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AC20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AD20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AE20" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AF20" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="AG20" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AH20" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI20" s="14" t="s">
-        <v>196</v>
+      <c r="E20" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="G20" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="I20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="K20" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="M20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="P20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q20" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="R20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="S20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="T20" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="U20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="V20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="W20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="X20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Y20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Z20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AA20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AB20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AC20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AD20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AE20" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AF20" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AG20" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AH20" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI20" s="15" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F21" s="13">
+      <c r="A21" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="F21" s="14">
         <v>1.0</v>
       </c>
       <c r="G21" s="16">
         <v>10.0</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="14">
         <v>97.0</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="14">
         <v>36.0</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="14">
         <v>84.0</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="18">
         <v>0.429</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="14">
         <v>28.0</v>
       </c>
-      <c r="M21" s="13">
+      <c r="M21" s="14">
         <v>61.0</v>
       </c>
-      <c r="N21" s="17">
+      <c r="N21" s="18">
         <v>0.459</v>
       </c>
-      <c r="O21" s="13">
+      <c r="O21" s="14">
         <v>8.0</v>
       </c>
-      <c r="P21" s="13">
+      <c r="P21" s="14">
         <v>23.0</v>
       </c>
-      <c r="Q21" s="17">
+      <c r="Q21" s="18">
         <v>0.348</v>
       </c>
-      <c r="R21" s="13">
+      <c r="R21" s="14">
         <v>17.0</v>
       </c>
-      <c r="S21" s="13">
+      <c r="S21" s="14">
         <v>21.0</v>
       </c>
-      <c r="T21" s="17">
+      <c r="T21" s="18">
         <v>0.81</v>
       </c>
-      <c r="U21" s="13">
+      <c r="U21" s="14">
         <v>12.0</v>
       </c>
-      <c r="V21" s="13">
+      <c r="V21" s="14">
         <v>35.0</v>
       </c>
-      <c r="W21" s="13">
+      <c r="W21" s="14">
         <v>47.0</v>
       </c>
-      <c r="X21" s="13">
+      <c r="X21" s="14">
         <v>24.0</v>
       </c>
-      <c r="Y21" s="13">
+      <c r="Y21" s="14">
         <v>12.0</v>
       </c>
-      <c r="Z21" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AA21" s="13">
+      <c r="Z21" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="AA21" s="14">
         <v>17.0</v>
       </c>
-      <c r="AB21" s="13">
+      <c r="AB21" s="14">
         <v>23.0</v>
       </c>
-      <c r="AC21" s="13">
+      <c r="AC21" s="14">
         <v>106.0</v>
       </c>
-      <c r="AD21" s="13">
+      <c r="AD21" s="14">
         <v>-3.0</v>
       </c>
-      <c r="AE21" s="17">
+      <c r="AE21" s="18">
         <v>0.476</v>
       </c>
-      <c r="AF21" s="17">
+      <c r="AF21" s="18">
         <v>0.52</v>
       </c>
-      <c r="AG21" s="13">
+      <c r="AG21" s="14">
         <v>1.41</v>
       </c>
-      <c r="AH21" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="AI21" s="14" t="s">
-        <v>203</v>
+      <c r="AH21" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="AI21" s="15" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>
